--- a/docs/data/jp/xlsx/6912.xlsx
+++ b/docs/data/jp/xlsx/6912.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC160"/>
+  <dimension ref="A1:AC167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4279,10 +4282,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>2710</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4317,7 +4322,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>8800000</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5516,7 +5523,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5768,1237 +5775,1271 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>1317.017</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>1301.819</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>1795.006</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>1244.228</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>1553.513</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>1624.367</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>2047.1</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>1571.648</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>1688.667</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>1798.227</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>2155.464</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>1771.742</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>1556.409</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>1830.282</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>1795.006</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>2047.1</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>2155.464</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>1550.182</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>1629.574</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>2047.312</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>1448.818</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>1699.393</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>1790.36</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>2021.51</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>1483.802</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>1854.465</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>2017.878</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>2117.767</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>2043.646</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>1410.43</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>1789.653</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>2047.312</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>2021.51</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>2117.767</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>1144.846</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>1208.913</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>1374.824</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>1138.521</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>1175.914</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>1243.812</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>1404.47</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>1205.937</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>1287.964</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>1279.169</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>1565.8</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>1334.747</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>1129.122</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>1219.662</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>1374.824</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>1404.47</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>1565.8</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>405.335</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>420.662</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>672.4880000000001</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>310.296</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>523.48</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>546.547</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>617.04</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>277.864</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>566.501</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>738.7089999999999</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>551.967</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>708.898</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>281.309</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>569.991</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>672.4880000000001</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>617.04</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>551.967</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.38</v>
+        <v>1144.846</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0.445</v>
+        <v>1208.913</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>0.384</v>
+        <v>1374.824</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0.495</v>
+        <v>1138.521</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0.841</v>
+        <v>1175.914</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0.831</v>
+        <v>1243.812</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>2.055</v>
+        <v>1404.47</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>0.709</v>
+        <v>1205.937</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>4.788</v>
+        <v>1287.964</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>2.344</v>
+        <v>1279.169</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>5.655</v>
+        <v>1565.8</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>3.597</v>
+        <v>1334.747</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>0.792</v>
+        <v>1129.122</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0.07099999999999999</v>
+        <v>1219.662</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0.384</v>
+        <v>1374.824</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>2.055</v>
+        <v>1404.47</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>5.655</v>
+        <v>1565.8</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>20.641</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>44.374</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>23.753</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>54.335</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>66.017</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>27.413</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>43.723</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>53.707</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>0.665</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>405.335</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>420.662</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>672.4880000000001</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>310.296</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>523.48</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>546.547</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>617.04</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>277.864</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>566.501</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>738.7089999999999</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>551.967</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>708.898</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>281.309</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>569.991</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>672.4880000000001</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>617.04</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>551.967</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>5.488</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>-4.503</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>0</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>7.239</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>3.642</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>3.055</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>5.056</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>5.461</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>2.283</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>5.231</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>4.035</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>3.598</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>6.271</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>4.898</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>1.792</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>3.055</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>5.231</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>0.9370000000000001</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>28.26</v>
+        <v>0.38</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>45.887</v>
+        <v>0.445</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>4.054</v>
+        <v>0.384</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>55.414</v>
+        <v>0.495</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>30.965</v>
+        <v>0.841</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>51.051</v>
+        <v>0.831</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>7.933</v>
+        <v>2.055</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>88.648</v>
+        <v>0.709</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>31.733</v>
+        <v>4.788</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>46.647</v>
+        <v>2.344</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>7.257</v>
+        <v>5.655</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>63.576</v>
+        <v>3.597</v>
       </c>
       <c r="T87" s="22" t="n">
-        <v>6.314</v>
+        <v>0.792</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>2.501</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>4.054</v>
+        <v>0.384</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>7.933</v>
+        <v>2.055</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>7.257</v>
+        <v>5.655</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>1.01</v>
+        <v>20.641</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>1.011</v>
+        <v>41.8</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>1.012</v>
+        <v>0.616</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>1.132</v>
+        <v>44.374</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>1.132</v>
+        <v>23.753</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>1.134</v>
+        <v>54.335</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>1.136</v>
+        <v>0.647</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>1.692</v>
+        <v>66.017</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>1.694</v>
+        <v>27.413</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>1.692</v>
+        <v>43.723</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>1.704</v>
+        <v>0.665</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>2.064</v>
+        <v>53.707</v>
       </c>
       <c r="T88" s="22" t="n">
-        <v>0.678</v>
+        <v>0.623</v>
       </c>
       <c r="U88" s="22" t="n">
-        <v>0.753</v>
+        <v>0.639</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>1.012</v>
+        <v>0.616</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>1.136</v>
+        <v>0.647</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>1.704</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>16.452</v>
-      </c>
-      <c r="D89" s="22" t="n">
-        <v>18.899</v>
-      </c>
-      <c r="E89" s="22" t="n">
-        <v>8.999000000000001</v>
+        <v>0</v>
       </c>
       <c r="F89" s="22" t="n">
+        <v>5.488</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J89" s="22" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K89" s="22" t="n">
+        <v>-4.503</v>
+      </c>
+      <c r="N89" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="G89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="22" t="n">
-        <v>13.643</v>
-      </c>
-      <c r="I89" s="22" t="n">
-        <v>-1.588</v>
-      </c>
-      <c r="J89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="22" t="n">
-        <v>2.781</v>
-      </c>
-      <c r="N89" s="22" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="T89" s="22" t="n">
-        <v>3.158</v>
-      </c>
-      <c r="U89" s="22" t="n">
-        <v>13.266</v>
-      </c>
-      <c r="V89" s="22" t="n">
-        <v>8.999000000000001</v>
-      </c>
-      <c r="W89" s="22" t="n">
-        <v>-1.588</v>
-      </c>
-      <c r="X89" s="22" t="n">
-        <v>2.781</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>0.5</v>
+        <v>7.239</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>3.642</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>3.055</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>0.499</v>
+        <v>5.056</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>0.5</v>
+        <v>5.461</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>0.5</v>
+        <v>2.283</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>0.5</v>
+        <v>5.231</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>0.499</v>
+        <v>14.4</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>0.5</v>
+        <v>4.035</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>0.5</v>
+        <v>3.598</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>16.501</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>0.499</v>
+        <v>6.271</v>
+      </c>
+      <c r="T90" s="22" t="n">
+        <v>4.898</v>
+      </c>
+      <c r="U90" s="22" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="V90" s="22" t="n">
+        <v>3.055</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>0.5</v>
+        <v>5.231</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>16.501</v>
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>0.109</v>
+        <v>28.26</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>1.581</v>
+        <v>45.887</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>-0.8139999999999999</v>
+        <v>4.054</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>0.044</v>
+        <v>55.414</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>0.294</v>
+        <v>30.965</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>0.85</v>
+        <v>51.051</v>
       </c>
       <c r="I91" s="22" t="n">
-        <v>0.599</v>
+        <v>7.933</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>0.8</v>
+        <v>88.648</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>0.063</v>
+        <v>31.733</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>0.734</v>
+        <v>46.647</v>
       </c>
       <c r="M91" s="22" t="n">
-        <v>4.043</v>
+        <v>7.257</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>0.001</v>
+        <v>63.576</v>
       </c>
       <c r="T91" s="22" t="n">
-        <v>-3.415</v>
+        <v>6.314</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>-1.285</v>
+        <v>2.501</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>-0.8139999999999999</v>
+        <v>4.054</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>0.599</v>
+        <v>7.933</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>4.043</v>
+        <v>7.257</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>18.072</v>
+        <v>1.01</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>20.49</v>
+        <v>1.011</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>11.199</v>
+        <v>1.012</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>1.677</v>
+        <v>1.132</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>1.926</v>
+        <v>1.132</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>16.127</v>
+        <v>1.134</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>0.647</v>
+        <v>1.136</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>2.992</v>
+        <v>1.692</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>2.257</v>
+        <v>1.694</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>8.339</v>
+        <v>1.692</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>25.028</v>
+        <v>1.704</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>6.076</v>
+        <v>2.064</v>
       </c>
       <c r="T92" s="22" t="n">
-        <v>5.948</v>
+        <v>0.678</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>30.735</v>
+        <v>0.753</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>11.199</v>
+        <v>1.012</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>0.647</v>
+        <v>1.136</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>25.028</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>415.524</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>446.058</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>665.342</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>364.034</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>552.518</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>581.472</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>624.326</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>363.521</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>595.976</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>777.0170000000001</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>534.196</v>
-      </c>
-      <c r="N93" s="12" t="n">
-        <v>766.399</v>
-      </c>
-      <c r="T93" s="12" t="n">
-        <v>281.674</v>
-      </c>
-      <c r="U93" s="12" t="n">
-        <v>541.758</v>
-      </c>
-      <c r="V93" s="12" t="n">
-        <v>665.342</v>
-      </c>
-      <c r="W93" s="12" t="n">
-        <v>624.326</v>
-      </c>
-      <c r="X93" s="12" t="n">
-        <v>534.196</v>
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n">
+        <v>16.452</v>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>18.899</v>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>8.999000000000001</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="22" t="n">
+        <v>13.643</v>
+      </c>
+      <c r="I93" s="22" t="n">
+        <v>-1.588</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="22" t="n">
+        <v>2.781</v>
+      </c>
+      <c r="N93" s="22" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="T93" s="22" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="U93" s="22" t="n">
+        <v>13.266</v>
+      </c>
+      <c r="V93" s="22" t="n">
+        <v>8.999000000000001</v>
+      </c>
+      <c r="W93" s="22" t="n">
+        <v>-1.588</v>
+      </c>
+      <c r="X93" s="22" t="n">
+        <v>2.781</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="n">
-        <v>415.524</v>
-      </c>
-      <c r="D94" s="12" t="n">
-        <v>446.058</v>
-      </c>
-      <c r="E94" s="12" t="n">
-        <v>665.342</v>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>364.034</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>552.518</v>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>581.472</v>
-      </c>
-      <c r="I94" s="12" t="n">
-        <v>624.326</v>
-      </c>
-      <c r="J94" s="12" t="n">
-        <v>363.521</v>
-      </c>
-      <c r="K94" s="12" t="n">
-        <v>595.976</v>
-      </c>
-      <c r="L94" s="12" t="n">
-        <v>777.0170000000001</v>
-      </c>
-      <c r="M94" s="12" t="n">
-        <v>534.196</v>
-      </c>
-      <c r="N94" s="12" t="n">
-        <v>766.399</v>
-      </c>
-      <c r="T94" s="12" t="n">
-        <v>281.674</v>
-      </c>
-      <c r="U94" s="12" t="n">
-        <v>557.284</v>
-      </c>
-      <c r="V94" s="12" t="n">
-        <v>665.342</v>
-      </c>
-      <c r="W94" s="12" t="n">
-        <v>624.326</v>
-      </c>
-      <c r="X94" s="12" t="n">
-        <v>534.196</v>
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M94" s="22" t="n">
+        <v>16.501</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="W94" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X94" s="22" t="n">
+        <v>16.501</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>법인세 등</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>111.067</v>
+        <v>0.109</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>140.858</v>
+        <v>1.581</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>189.863</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>155.234</v>
+        <v>0.044</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>164.459</v>
+        <v>0.294</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>180.868</v>
+        <v>0.85</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>181.864</v>
+        <v>0.599</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>106.26</v>
+        <v>0.8</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>230.328</v>
+        <v>0.063</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>233.719</v>
+        <v>0.734</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>91.16500000000001</v>
+        <v>4.043</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>238.636</v>
+        <v>0.001</v>
       </c>
       <c r="T95" s="22" t="n">
-        <v>102.292</v>
+        <v>-3.415</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>150.172</v>
+        <v>-1.285</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>189.863</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>181.864</v>
+        <v>0.599</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>91.16500000000001</v>
+        <v>4.043</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="n">
-        <v>304.458</v>
-      </c>
-      <c r="D96" s="12" t="n">
-        <v>305.2</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>475.479</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>208.799</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>388.059</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>400.604</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>442.462</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>257.26</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>365.648</v>
-      </c>
-      <c r="L96" s="12" t="n">
-        <v>543.299</v>
-      </c>
-      <c r="M96" s="12" t="n">
-        <v>443.031</v>
-      </c>
-      <c r="N96" s="12" t="n">
-        <v>527.763</v>
-      </c>
-      <c r="T96" s="12" t="n">
-        <v>179.382</v>
-      </c>
-      <c r="U96" s="12" t="n">
-        <v>407.111</v>
-      </c>
-      <c r="V96" s="12" t="n">
-        <v>475.479</v>
-      </c>
-      <c r="W96" s="12" t="n">
-        <v>442.462</v>
-      </c>
-      <c r="X96" s="12" t="n">
-        <v>443.031</v>
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C96" s="22" t="n">
+        <v>18.072</v>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>11.199</v>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>1.926</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>16.127</v>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J96" s="22" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>8.339</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>25.028</v>
+      </c>
+      <c r="N96" s="22" t="n">
+        <v>6.076</v>
+      </c>
+      <c r="T96" s="22" t="n">
+        <v>5.948</v>
+      </c>
+      <c r="U96" s="22" t="n">
+        <v>30.735</v>
+      </c>
+      <c r="V96" s="22" t="n">
+        <v>11.199</v>
+      </c>
+      <c r="W96" s="22" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="X96" s="22" t="n">
+        <v>25.028</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>경상이익</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>304.458</v>
+        <v>415.524</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>305.2</v>
+        <v>446.058</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>475.479</v>
+        <v>665.342</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>208.799</v>
+        <v>364.034</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>388.059</v>
+        <v>552.518</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>400.604</v>
+        <v>581.472</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>442.462</v>
+        <v>624.326</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>257.26</v>
+        <v>363.521</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>365.648</v>
+        <v>595.976</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>543.299</v>
+        <v>777.0170000000001</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>443.031</v>
+        <v>534.196</v>
       </c>
       <c r="N97" s="12" t="n">
-        <v>527.763</v>
+        <v>766.399</v>
       </c>
       <c r="T97" s="12" t="n">
-        <v>179.382</v>
+        <v>281.674</v>
       </c>
       <c r="U97" s="12" t="n">
-        <v>407.111</v>
+        <v>541.758</v>
       </c>
       <c r="V97" s="12" t="n">
-        <v>475.479</v>
+        <v>665.342</v>
       </c>
       <c r="W97" s="12" t="n">
-        <v>442.462</v>
+        <v>624.326</v>
       </c>
       <c r="X97" s="12" t="n">
-        <v>443.031</v>
+        <v>534.196</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G98" s="17">
+        <f>IF(OR(G97="",C97=""),"",IF(C97&lt;=0,"",IFERROR(G97/C97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H98" s="17">
+        <f>IF(OR(H97="",D97=""),"",IF(D97&lt;=0,"",IFERROR(H97/D97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I98" s="17">
+        <f>IF(OR(I97="",E97=""),"",IF(E97&lt;=0,"",IFERROR(I97/E97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J98" s="17">
+        <f>IF(OR(J97="",F97=""),"",IF(F97&lt;=0,"",IFERROR(J97/F97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF(OR(K97="",G97=""),"",IF(G97&lt;=0,"",IFERROR(K97/G97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L98" s="17">
+        <f>IF(OR(L97="",H97=""),"",IF(H97&lt;=0,"",IFERROR(L97/H97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M98" s="17">
+        <f>IF(OR(M97="",I97=""),"",IF(I97&lt;=0,"",IFERROR(M97/I97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N98" s="17">
+        <f>IF(OR(N97="",J97=""),"",IF(J97&lt;=0,"",IFERROR(N97/J97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T98" s="17">
+        <f>IF(OR(T97="",S97=""),"",IF(S97&lt;=0,"",IFERROR(T97/S97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U98" s="17">
+        <f>IF(OR(U97="",T97=""),"",IF(T97&lt;=0,"",IFERROR(U97/T97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V98" s="17">
+        <f>IF(OR(V97="",U97=""),"",IF(U97&lt;=0,"",IFERROR(V97/U97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W98" s="17">
+        <f>IF(OR(W97="",V97=""),"",IF(V97&lt;=0,"",IFERROR(W97/V97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X98" s="17">
+        <f>IF(OR(X97="",W97=""),"",IF(W97&lt;=0,"",IFERROR(X97/W97-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B99" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="n"/>
-      <c r="D99" s="18" t="n"/>
-      <c r="E99" s="18" t="n"/>
-      <c r="F99" s="18" t="n"/>
-      <c r="G99" s="18" t="n"/>
-      <c r="H99" s="18" t="n"/>
-      <c r="I99" s="18" t="n"/>
-      <c r="J99" s="18" t="n"/>
-      <c r="K99" s="18" t="n"/>
-      <c r="L99" s="18" t="n"/>
-      <c r="M99" s="18" t="n"/>
-      <c r="N99" s="18" t="n"/>
-      <c r="O99" s="18" t="n"/>
-      <c r="P99" s="18" t="n"/>
-      <c r="Q99" s="18" t="n"/>
-      <c r="R99" s="18" t="n"/>
-      <c r="S99" s="18" t="n"/>
-      <c r="T99" s="18" t="n"/>
-      <c r="U99" s="18" t="n"/>
-      <c r="V99" s="18" t="n"/>
-      <c r="W99" s="18" t="n"/>
-      <c r="X99" s="18" t="n"/>
-      <c r="Y99" s="18" t="n"/>
-      <c r="Z99" s="18" t="n"/>
-      <c r="AA99" s="18" t="n"/>
-      <c r="AB99" s="18" t="n"/>
-      <c r="AC99" s="18" t="n"/>
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>415.524</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>446.058</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>665.342</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>364.034</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>552.518</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>581.472</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>624.326</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>363.521</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>595.976</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>777.0170000000001</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>534.196</v>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>766.399</v>
+      </c>
+      <c r="T99" s="12" t="n">
+        <v>281.674</v>
+      </c>
+      <c r="U99" s="12" t="n">
+        <v>557.284</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>665.342</v>
+      </c>
+      <c r="W99" s="12" t="n">
+        <v>624.326</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>534.196</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L100" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M100" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N100" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O100" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P100" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q100" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R100" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S100" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T100" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U100" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V100" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W100" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X100" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y100" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z100" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA100" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB100" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC100" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="n">
+        <v>111.067</v>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>140.858</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>189.863</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>155.234</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>164.459</v>
+      </c>
+      <c r="H100" s="22" t="n">
+        <v>180.868</v>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>181.864</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>106.26</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>230.328</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>233.719</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>91.16500000000001</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>238.636</v>
+      </c>
+      <c r="T100" s="22" t="n">
+        <v>102.292</v>
+      </c>
+      <c r="U100" s="22" t="n">
+        <v>150.172</v>
+      </c>
+      <c r="V100" s="22" t="n">
+        <v>189.863</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>181.864</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>91.16500000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7060,2812 +7101,3242 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>54.379</v>
-      </c>
-      <c r="D102" s="22" t="n">
-        <v>-64.83799999999999</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>173.433</v>
-      </c>
-      <c r="F102" s="22" t="n">
-        <v>-98.402</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>-174.022</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>-27.304</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>-7.243</v>
-      </c>
-      <c r="J102" s="22" t="n">
-        <v>120.182</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>65.258</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>69.666</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="N102" s="22" t="n">
-        <v>103.925</v>
-      </c>
-      <c r="T102" s="22" t="n">
-        <v>95.694</v>
-      </c>
-      <c r="U102" s="22" t="n">
-        <v>127.688</v>
-      </c>
-      <c r="V102" s="22" t="n">
-        <v>173.433</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>-7.243</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>1.878</v>
+      <c r="A102" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G102" s="17">
+        <f>IF(OR(G101="",C101=""),"",IF(C101&lt;=0,"",IFERROR(G101/C101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H102" s="17">
+        <f>IF(OR(H101="",D101=""),"",IF(D101&lt;=0,"",IFERROR(H101/D101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I102" s="17">
+        <f>IF(OR(I101="",E101=""),"",IF(E101&lt;=0,"",IFERROR(I101/E101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J102" s="17">
+        <f>IF(OR(J101="",F101=""),"",IF(F101&lt;=0,"",IFERROR(J101/F101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF(OR(K101="",G101=""),"",IF(G101&lt;=0,"",IFERROR(K101/G101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L102" s="17">
+        <f>IF(OR(L101="",H101=""),"",IF(H101&lt;=0,"",IFERROR(L101/H101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M102" s="17">
+        <f>IF(OR(M101="",I101=""),"",IF(I101&lt;=0,"",IFERROR(M101/I101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N102" s="17">
+        <f>IF(OR(N101="",J101=""),"",IF(J101&lt;=0,"",IFERROR(N101/J101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T102" s="17">
+        <f>IF(OR(T101="",S101=""),"",IF(S101&lt;=0,"",IFERROR(T101/S101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U102" s="17">
+        <f>IF(OR(U101="",T101=""),"",IF(T101&lt;=0,"",IFERROR(U101/T101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V102" s="17">
+        <f>IF(OR(V101="",U101=""),"",IF(U101&lt;=0,"",IFERROR(V101/U101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W102" s="17">
+        <f>IF(OR(W101="",V101=""),"",IF(V101&lt;=0,"",IFERROR(W101/V101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X102" s="17">
+        <f>IF(OR(X101="",W101=""),"",IF(W101&lt;=0,"",IFERROR(X101/W101-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="C103" s="22" t="n">
-        <v>29.08</v>
-      </c>
-      <c r="D103" s="22" t="n">
-        <v>-33.287</v>
-      </c>
-      <c r="E103" s="22" t="n">
-        <v>51.854</v>
-      </c>
-      <c r="F103" s="22" t="n">
-        <v>74.672</v>
-      </c>
-      <c r="G103" s="22" t="n">
-        <v>-117.093</v>
-      </c>
-      <c r="H103" s="22" t="n">
-        <v>96.932</v>
-      </c>
-      <c r="I103" s="22" t="n">
-        <v>-71.28400000000001</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>-22.398</v>
-      </c>
-      <c r="K103" s="22" t="n">
-        <v>25.639</v>
-      </c>
-      <c r="L103" s="22" t="n">
-        <v>94.91800000000001</v>
-      </c>
-      <c r="M103" s="22" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="N103" s="22" t="n">
-        <v>48.546</v>
-      </c>
-      <c r="T103" s="22" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="U103" s="22" t="n">
-        <v>16.101</v>
-      </c>
-      <c r="V103" s="22" t="n">
-        <v>51.854</v>
-      </c>
-      <c r="W103" s="22" t="n">
-        <v>-71.28400000000001</v>
-      </c>
-      <c r="X103" s="22" t="n">
-        <v>41.19</v>
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>304.458</v>
+      </c>
+      <c r="D103" s="12" t="n">
+        <v>305.2</v>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>475.479</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>208.799</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>388.059</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>400.604</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>442.462</v>
+      </c>
+      <c r="J103" s="12" t="n">
+        <v>257.26</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>365.648</v>
+      </c>
+      <c r="L103" s="12" t="n">
+        <v>543.299</v>
+      </c>
+      <c r="M103" s="12" t="n">
+        <v>443.031</v>
+      </c>
+      <c r="N103" s="12" t="n">
+        <v>527.763</v>
+      </c>
+      <c r="T103" s="12" t="n">
+        <v>179.382</v>
+      </c>
+      <c r="U103" s="12" t="n">
+        <v>407.111</v>
+      </c>
+      <c r="V103" s="12" t="n">
+        <v>475.479</v>
+      </c>
+      <c r="W103" s="12" t="n">
+        <v>442.462</v>
+      </c>
+      <c r="X103" s="12" t="n">
+        <v>443.031</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여 조정액</t>
-        </is>
-      </c>
-      <c r="C104" s="22" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>-0.981</v>
-      </c>
-      <c r="E104" s="22" t="n">
-        <v>38.279</v>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>-3.257</v>
-      </c>
-      <c r="G104" s="22" t="n">
-        <v>-3.258</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>-3.258</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>33.774</v>
-      </c>
-      <c r="J104" s="22" t="n">
-        <v>-6.242</v>
-      </c>
-      <c r="K104" s="22" t="n">
-        <v>-6.242</v>
-      </c>
-      <c r="L104" s="22" t="n">
-        <v>-6.242</v>
-      </c>
-      <c r="M104" s="22" t="n">
-        <v>56.96</v>
-      </c>
-      <c r="N104" s="22" t="n">
-        <v>-7.676</v>
-      </c>
-      <c r="T104" s="22" t="n">
-        <v>6.567</v>
-      </c>
-      <c r="U104" s="22" t="n">
-        <v>6.086</v>
-      </c>
-      <c r="V104" s="22" t="n">
-        <v>38.279</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>33.774</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>56.96</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C105" s="22" t="n">
-        <v>82.479</v>
-      </c>
-      <c r="D105" s="22" t="n">
-        <v>-99.105</v>
-      </c>
-      <c r="E105" s="22" t="n">
-        <v>263.566</v>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>-26.987</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>-294.373</v>
-      </c>
-      <c r="H105" s="22" t="n">
-        <v>66.37</v>
-      </c>
-      <c r="I105" s="22" t="n">
-        <v>-44.753</v>
-      </c>
-      <c r="J105" s="22" t="n">
-        <v>91.541</v>
-      </c>
-      <c r="K105" s="22" t="n">
-        <v>84.657</v>
-      </c>
-      <c r="L105" s="22" t="n">
-        <v>158.342</v>
-      </c>
-      <c r="M105" s="22" t="n">
-        <v>100.028</v>
-      </c>
-      <c r="N105" s="22" t="n">
-        <v>144.795</v>
-      </c>
-      <c r="T105" s="22" t="n">
-        <v>151.522</v>
-      </c>
-      <c r="U105" s="22" t="n">
-        <v>149.877</v>
-      </c>
-      <c r="V105" s="22" t="n">
-        <v>263.566</v>
-      </c>
-      <c r="W105" s="22" t="n">
-        <v>-44.753</v>
-      </c>
-      <c r="X105" s="22" t="n">
-        <v>100.028</v>
+      <c r="A104" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G104" s="17">
+        <f>IF(OR(G103="",C103=""),"",IF(C103&lt;=0,"",IFERROR(G103/C103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H104" s="17">
+        <f>IF(OR(H103="",D103=""),"",IF(D103&lt;=0,"",IFERROR(H103/D103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I104" s="17">
+        <f>IF(OR(I103="",E103=""),"",IF(E103&lt;=0,"",IFERROR(I103/E103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J104" s="17">
+        <f>IF(OR(J103="",F103=""),"",IF(F103&lt;=0,"",IFERROR(J103/F103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K104" s="17">
+        <f>IF(OR(K103="",G103=""),"",IF(G103&lt;=0,"",IFERROR(K103/G103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L104" s="17">
+        <f>IF(OR(L103="",H103=""),"",IF(H103&lt;=0,"",IFERROR(L103/H103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M104" s="17">
+        <f>IF(OR(M103="",I103=""),"",IF(I103&lt;=0,"",IFERROR(M103/I103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N104" s="17">
+        <f>IF(OR(N103="",J103=""),"",IF(J103&lt;=0,"",IFERROR(N103/J103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T104" s="17">
+        <f>IF(OR(T103="",S103=""),"",IF(S103&lt;=0,"",IFERROR(T103/S103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U104" s="17">
+        <f>IF(OR(U103="",T103=""),"",IF(T103&lt;=0,"",IFERROR(U103/T103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V104" s="17">
+        <f>IF(OR(V103="",U103=""),"",IF(U103&lt;=0,"",IFERROR(V103/U103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W104" s="17">
+        <f>IF(OR(W103="",V103=""),"",IF(V103&lt;=0,"",IFERROR(W103/V103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X104" s="17">
+        <f>IF(OR(X103="",W103=""),"",IF(W103&lt;=0,"",IFERROR(X103/W103-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="n">
-        <v>386.936</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>206.095</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>739.045</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>181.811</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>93.687</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>466.974</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>397.708</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>348.802</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>450.304</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>701.641</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>543.059</v>
-      </c>
-      <c r="N106" s="12" t="n">
-        <v>672.558</v>
-      </c>
-      <c r="T106" s="12" t="n">
-        <v>330.904</v>
-      </c>
-      <c r="U106" s="12" t="n">
-        <v>556.9880000000001</v>
-      </c>
-      <c r="V106" s="12" t="n">
-        <v>739.045</v>
-      </c>
-      <c r="W106" s="12" t="n">
-        <v>397.708</v>
-      </c>
-      <c r="X106" s="12" t="n">
-        <v>543.059</v>
-      </c>
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B106" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="18" t="n"/>
+      <c r="G106" s="18" t="n"/>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
+      <c r="J106" s="18" t="n"/>
+      <c r="K106" s="18" t="n"/>
+      <c r="L106" s="18" t="n"/>
+      <c r="M106" s="18" t="n"/>
+      <c r="N106" s="18" t="n"/>
+      <c r="O106" s="18" t="n"/>
+      <c r="P106" s="18" t="n"/>
+      <c r="Q106" s="18" t="n"/>
+      <c r="R106" s="18" t="n"/>
+      <c r="S106" s="18" t="n"/>
+      <c r="T106" s="18" t="n"/>
+      <c r="U106" s="18" t="n"/>
+      <c r="V106" s="18" t="n"/>
+      <c r="W106" s="18" t="n"/>
+      <c r="X106" s="18" t="n"/>
+      <c r="Y106" s="18" t="n"/>
+      <c r="Z106" s="18" t="n"/>
+      <c r="AA106" s="18" t="n"/>
+      <c r="AB106" s="18" t="n"/>
+      <c r="AC106" s="18" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="n">
-        <v>386.936</v>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>206.095</v>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>739.045</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>181.811</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>93.687</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>466.974</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>397.708</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>348.802</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>450.304</v>
-      </c>
-      <c r="L107" s="12" t="n">
-        <v>701.641</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>543.059</v>
-      </c>
-      <c r="N107" s="12" t="n">
-        <v>672.558</v>
-      </c>
-      <c r="T107" s="12" t="n">
-        <v>330.904</v>
-      </c>
-      <c r="U107" s="12" t="n">
-        <v>556.9880000000001</v>
-      </c>
-      <c r="V107" s="12" t="n">
-        <v>739.045</v>
-      </c>
-      <c r="W107" s="12" t="n">
-        <v>397.708</v>
-      </c>
-      <c r="X107" s="12" t="n">
-        <v>543.059</v>
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O107" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P107" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q107" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R107" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S107" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T107" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U107" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V107" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W107" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X107" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y107" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z107" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA107" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB107" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC107" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>304.458</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>305.2</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>475.479</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>208.799</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>388.059</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>400.604</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>442.462</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>257.26</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>365.648</v>
+      </c>
+      <c r="L108" s="12" t="n">
+        <v>543.299</v>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>443.031</v>
+      </c>
+      <c r="N108" s="12" t="n">
+        <v>527.763</v>
+      </c>
+      <c r="T108" s="12" t="n">
+        <v>179.382</v>
+      </c>
+      <c r="U108" s="12" t="n">
+        <v>407.111</v>
+      </c>
+      <c r="V108" s="12" t="n">
+        <v>475.479</v>
+      </c>
+      <c r="W108" s="12" t="n">
+        <v>442.462</v>
+      </c>
+      <c r="X108" s="12" t="n">
+        <v>443.031</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="n">
+        <v>54.379</v>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>-64.83799999999999</v>
+      </c>
+      <c r="E109" s="22" t="n">
+        <v>173.433</v>
+      </c>
+      <c r="F109" s="22" t="n">
+        <v>-98.402</v>
+      </c>
+      <c r="G109" s="22" t="n">
+        <v>-174.022</v>
+      </c>
+      <c r="H109" s="22" t="n">
+        <v>-27.304</v>
+      </c>
+      <c r="I109" s="22" t="n">
+        <v>-7.243</v>
+      </c>
+      <c r="J109" s="22" t="n">
+        <v>120.182</v>
+      </c>
+      <c r="K109" s="22" t="n">
+        <v>65.258</v>
+      </c>
+      <c r="L109" s="22" t="n">
+        <v>69.666</v>
+      </c>
+      <c r="M109" s="22" t="n">
+        <v>1.878</v>
+      </c>
+      <c r="N109" s="22" t="n">
+        <v>103.925</v>
+      </c>
+      <c r="T109" s="22" t="n">
+        <v>95.694</v>
+      </c>
+      <c r="U109" s="22" t="n">
+        <v>127.688</v>
+      </c>
+      <c r="V109" s="22" t="n">
+        <v>173.433</v>
+      </c>
+      <c r="W109" s="22" t="n">
+        <v>-7.243</v>
+      </c>
+      <c r="X109" s="22" t="n">
+        <v>1.878</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>-33.287</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>51.854</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>74.672</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>-117.093</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>96.932</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>-71.28400000000001</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>-22.398</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>25.639</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>94.91800000000001</v>
+      </c>
+      <c r="M110" s="22" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="N110" s="22" t="n">
+        <v>48.546</v>
+      </c>
+      <c r="T110" s="22" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="U110" s="22" t="n">
+        <v>16.101</v>
+      </c>
+      <c r="V110" s="22" t="n">
+        <v>51.854</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>-71.28400000000001</v>
+      </c>
+      <c r="X110" s="22" t="n">
+        <v>41.19</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20" t="inlineStr">
+        <is>
+          <t>퇴직급여 조정액</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>-0.981</v>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>38.279</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>-3.257</v>
+      </c>
+      <c r="G111" s="22" t="n">
+        <v>-3.258</v>
+      </c>
+      <c r="H111" s="22" t="n">
+        <v>-3.258</v>
+      </c>
+      <c r="I111" s="22" t="n">
+        <v>33.774</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>-6.242</v>
+      </c>
+      <c r="K111" s="22" t="n">
+        <v>-6.242</v>
+      </c>
+      <c r="L111" s="22" t="n">
+        <v>-6.242</v>
+      </c>
+      <c r="M111" s="22" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="N111" s="22" t="n">
+        <v>-7.676</v>
+      </c>
+      <c r="T111" s="22" t="n">
+        <v>6.567</v>
+      </c>
+      <c r="U111" s="22" t="n">
+        <v>6.086</v>
+      </c>
+      <c r="V111" s="22" t="n">
+        <v>38.279</v>
+      </c>
+      <c r="W111" s="22" t="n">
+        <v>33.774</v>
+      </c>
+      <c r="X111" s="22" t="n">
+        <v>56.96</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>기타포괄손익 합계</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="n">
+        <v>82.479</v>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>-99.105</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>263.566</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>-26.987</v>
+      </c>
+      <c r="G112" s="22" t="n">
+        <v>-294.373</v>
+      </c>
+      <c r="H112" s="22" t="n">
+        <v>66.37</v>
+      </c>
+      <c r="I112" s="22" t="n">
+        <v>-44.753</v>
+      </c>
+      <c r="J112" s="22" t="n">
+        <v>91.541</v>
+      </c>
+      <c r="K112" s="22" t="n">
+        <v>84.657</v>
+      </c>
+      <c r="L112" s="22" t="n">
+        <v>158.342</v>
+      </c>
+      <c r="M112" s="22" t="n">
+        <v>100.028</v>
+      </c>
+      <c r="N112" s="22" t="n">
+        <v>144.795</v>
+      </c>
+      <c r="T112" s="22" t="n">
+        <v>151.522</v>
+      </c>
+      <c r="U112" s="22" t="n">
+        <v>149.877</v>
+      </c>
+      <c r="V112" s="22" t="n">
+        <v>263.566</v>
+      </c>
+      <c r="W112" s="22" t="n">
+        <v>-44.753</v>
+      </c>
+      <c r="X112" s="22" t="n">
+        <v>100.028</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>386.936</v>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>206.095</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>739.045</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>181.811</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>93.687</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>466.974</v>
+      </c>
+      <c r="I113" s="12" t="n">
+        <v>397.708</v>
+      </c>
+      <c r="J113" s="12" t="n">
+        <v>348.802</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>450.304</v>
+      </c>
+      <c r="L113" s="12" t="n">
+        <v>701.641</v>
+      </c>
+      <c r="M113" s="12" t="n">
+        <v>543.059</v>
+      </c>
+      <c r="N113" s="12" t="n">
+        <v>672.558</v>
+      </c>
+      <c r="T113" s="12" t="n">
+        <v>330.904</v>
+      </c>
+      <c r="U113" s="12" t="n">
+        <v>556.9880000000001</v>
+      </c>
+      <c r="V113" s="12" t="n">
+        <v>739.045</v>
+      </c>
+      <c r="W113" s="12" t="n">
+        <v>397.708</v>
+      </c>
+      <c r="X113" s="12" t="n">
+        <v>543.059</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>386.936</v>
+      </c>
+      <c r="D114" s="12" t="n">
+        <v>206.095</v>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>739.045</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>181.811</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>93.687</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>466.974</v>
+      </c>
+      <c r="I114" s="12" t="n">
+        <v>397.708</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>348.802</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>450.304</v>
+      </c>
+      <c r="L114" s="12" t="n">
+        <v>701.641</v>
+      </c>
+      <c r="M114" s="12" t="n">
+        <v>543.059</v>
+      </c>
+      <c r="N114" s="12" t="n">
+        <v>672.558</v>
+      </c>
+      <c r="T114" s="12" t="n">
+        <v>330.904</v>
+      </c>
+      <c r="U114" s="12" t="n">
+        <v>556.9880000000001</v>
+      </c>
+      <c r="V114" s="12" t="n">
+        <v>739.045</v>
+      </c>
+      <c r="W114" s="12" t="n">
+        <v>397.708</v>
+      </c>
+      <c r="X114" s="12" t="n">
+        <v>543.059</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C108" s="12" t="n">
+      <c r="C115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="12" t="n">
+      <c r="D115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="12" t="n">
+      <c r="E115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="12" t="n">
+      <c r="F115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="12" t="n">
+      <c r="G115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H108" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I108" s="12" t="n">
+      <c r="I115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="12" t="n">
+      <c r="J115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K108" s="12" t="n">
+      <c r="K115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L108" s="12" t="n">
+      <c r="L115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M108" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N108" s="12" t="n">
+      <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="T108" s="12" t="n">
+      <c r="T115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="U108" s="12" t="n">
+      <c r="U115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="12" t="n">
+      <c r="V115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="W108" s="12" t="n">
+      <c r="W115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="12" t="n">
+      <c r="X115" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="18" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B110" s="44" t="inlineStr">
+      <c r="B117" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C110" s="18" t="n"/>
-      <c r="D110" s="18" t="n"/>
-      <c r="E110" s="18" t="n"/>
-      <c r="F110" s="18" t="n"/>
-      <c r="G110" s="18" t="n"/>
-      <c r="H110" s="18" t="n"/>
-      <c r="I110" s="18" t="n"/>
-      <c r="J110" s="18" t="n"/>
-      <c r="K110" s="18" t="n"/>
-      <c r="L110" s="18" t="n"/>
-      <c r="M110" s="18" t="n"/>
-      <c r="N110" s="18" t="n"/>
-      <c r="O110" s="18" t="n"/>
-      <c r="P110" s="18" t="n"/>
-      <c r="Q110" s="18" t="n"/>
-      <c r="R110" s="18" t="n"/>
-      <c r="S110" s="18" t="n"/>
-      <c r="T110" s="18" t="n"/>
-      <c r="U110" s="18" t="n"/>
-      <c r="V110" s="18" t="n"/>
-      <c r="W110" s="18" t="n"/>
-      <c r="X110" s="18" t="n"/>
-      <c r="Y110" s="18" t="n"/>
-      <c r="Z110" s="18" t="n"/>
-      <c r="AA110" s="18" t="n"/>
-      <c r="AB110" s="18" t="n"/>
-      <c r="AC110" s="18" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="C117" s="18" t="n"/>
+      <c r="D117" s="18" t="n"/>
+      <c r="E117" s="18" t="n"/>
+      <c r="F117" s="18" t="n"/>
+      <c r="G117" s="18" t="n"/>
+      <c r="H117" s="18" t="n"/>
+      <c r="I117" s="18" t="n"/>
+      <c r="J117" s="18" t="n"/>
+      <c r="K117" s="18" t="n"/>
+      <c r="L117" s="18" t="n"/>
+      <c r="M117" s="18" t="n"/>
+      <c r="N117" s="18" t="n"/>
+      <c r="O117" s="18" t="n"/>
+      <c r="P117" s="18" t="n"/>
+      <c r="Q117" s="18" t="n"/>
+      <c r="R117" s="18" t="n"/>
+      <c r="S117" s="18" t="n"/>
+      <c r="T117" s="18" t="n"/>
+      <c r="U117" s="18" t="n"/>
+      <c r="V117" s="18" t="n"/>
+      <c r="W117" s="18" t="n"/>
+      <c r="X117" s="18" t="n"/>
+      <c r="Y117" s="18" t="n"/>
+      <c r="Z117" s="18" t="n"/>
+      <c r="AA117" s="18" t="n"/>
+      <c r="AB117" s="18" t="n"/>
+      <c r="AC117" s="18" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="H118" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J111" s="5" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K111" s="5" t="inlineStr">
+      <c r="K118" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L111" s="5" t="inlineStr">
+      <c r="L118" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M111" s="5" t="inlineStr">
+      <c r="M118" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N111" s="5" t="inlineStr">
+      <c r="N118" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O111" s="5" t="inlineStr">
+      <c r="O118" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P111" s="5" t="inlineStr">
+      <c r="P118" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q111" s="5" t="inlineStr">
+      <c r="Q118" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R111" s="5" t="inlineStr">
+      <c r="R118" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S111" s="5" t="inlineStr">
+      <c r="S118" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T111" s="5" t="inlineStr">
+      <c r="T118" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U111" s="5" t="inlineStr">
+      <c r="U118" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V111" s="5" t="inlineStr">
+      <c r="V118" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W111" s="5" t="inlineStr">
+      <c r="W118" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X111" s="5" t="inlineStr">
+      <c r="X118" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y111" s="5" t="inlineStr">
+      <c r="Y118" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z111" s="5" t="inlineStr">
+      <c r="Z118" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA111" s="5" t="inlineStr">
+      <c r="AA118" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB111" s="5" t="inlineStr">
+      <c r="AB118" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC111" s="5" t="inlineStr">
+      <c r="AC118" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C112" s="12" t="n">
+      <c r="C119" s="12" t="n">
         <v>808.011</v>
       </c>
-      <c r="E112" s="12" t="n">
+      <c r="E119" s="12" t="n">
         <v>1919.411</v>
       </c>
-      <c r="G112" s="12" t="n">
+      <c r="G119" s="12" t="n">
         <v>916.552</v>
       </c>
-      <c r="I112" s="12" t="n">
+      <c r="I119" s="12" t="n">
         <v>2122.35</v>
       </c>
-      <c r="K112" s="12" t="n">
+      <c r="K119" s="12" t="n">
         <v>959.497</v>
       </c>
-      <c r="M112" s="12" t="n">
+      <c r="M119" s="12" t="n">
         <v>2270.71</v>
       </c>
-      <c r="O112" s="12" t="n">
+      <c r="O119" s="12" t="n">
         <v>553.3680000000001</v>
       </c>
-      <c r="P112" s="12" t="n">
+      <c r="P119" s="12" t="n">
         <v>468.109</v>
       </c>
-      <c r="Q112" s="12" t="n">
+      <c r="Q119" s="12" t="n">
         <v>675.375</v>
       </c>
-      <c r="R112" s="12" t="n">
+      <c r="R119" s="12" t="n">
         <v>699.211</v>
       </c>
-      <c r="S112" s="12" t="n">
+      <c r="S119" s="12" t="n">
         <v>460.158</v>
       </c>
-      <c r="T112" s="12" t="n">
+      <c r="T119" s="12" t="n">
         <v>1087.815</v>
       </c>
-      <c r="U112" s="12" t="n">
+      <c r="U119" s="12" t="n">
         <v>1544.221</v>
       </c>
-      <c r="V112" s="12" t="n">
+      <c r="V119" s="12" t="n">
         <v>1919.411</v>
       </c>
-      <c r="W112" s="12" t="n">
+      <c r="W119" s="12" t="n">
         <v>2122.35</v>
       </c>
-      <c r="X112" s="12" t="n">
+      <c r="X119" s="12" t="n">
         <v>2270.71</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C113" s="22" t="n">
-        <v>128.71</v>
-      </c>
-      <c r="E113" s="22" t="n">
-        <v>276.554</v>
-      </c>
-      <c r="G113" s="22" t="n">
-        <v>133.257</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>282.322</v>
-      </c>
-      <c r="K113" s="22" t="n">
-        <v>123.956</v>
-      </c>
-      <c r="M113" s="22" t="n">
-        <v>277.364</v>
-      </c>
-      <c r="O113" s="22" t="n">
-        <v>174.903</v>
-      </c>
-      <c r="P113" s="22" t="n">
-        <v>184.337</v>
-      </c>
-      <c r="Q113" s="22" t="n">
-        <v>219.436</v>
-      </c>
-      <c r="R113" s="22" t="n">
-        <v>257.033</v>
-      </c>
-      <c r="S113" s="22" t="n">
-        <v>280.818</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>269.007</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>259.703</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>276.554</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>282.322</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>277.364</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>주식보상비용</t>
-        </is>
-      </c>
-      <c r="C114" s="22" t="n">
-        <v>16.059</v>
-      </c>
-      <c r="E114" s="22" t="n">
-        <v>31.956</v>
-      </c>
-      <c r="G114" s="22" t="n">
-        <v>14.471</v>
-      </c>
-      <c r="I114" s="22" t="n">
-        <v>27.517</v>
-      </c>
-      <c r="K114" s="22" t="n">
-        <v>13.509</v>
-      </c>
-      <c r="M114" s="22" t="n">
-        <v>27.482</v>
-      </c>
-      <c r="Q114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" s="22" t="n">
-        <v>18.898</v>
-      </c>
-      <c r="S114" s="22" t="n">
-        <v>25.197</v>
-      </c>
-      <c r="T114" s="22" t="n">
-        <v>27.446</v>
-      </c>
-      <c r="U114" s="22" t="n">
-        <v>27.134</v>
-      </c>
-      <c r="V114" s="22" t="n">
-        <v>31.956</v>
-      </c>
-      <c r="W114" s="22" t="n">
-        <v>27.517</v>
-      </c>
-      <c r="X114" s="22" t="n">
-        <v>27.482</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="O115" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" s="22" t="n">
-        <v>1.606</v>
-      </c>
-      <c r="Q115" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" s="22" t="n">
-        <v>-1.575</v>
-      </c>
-      <c r="S115" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여자산 증감</t>
-        </is>
-      </c>
-      <c r="E116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="22" t="n">
-        <v>-36.368</v>
-      </c>
-      <c r="K116" s="22" t="n">
-        <v>-22.237</v>
-      </c>
-      <c r="M116" s="22" t="n">
-        <v>-43.593</v>
-      </c>
-      <c r="V116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="22" t="n">
-        <v>-36.368</v>
-      </c>
-      <c r="X116" s="22" t="n">
-        <v>-43.593</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="C117" s="22" t="n">
-        <v>-13.743</v>
-      </c>
-      <c r="E117" s="22" t="n">
-        <v>-27.436</v>
-      </c>
-      <c r="G117" s="22" t="n">
-        <v>-19.118</v>
-      </c>
-      <c r="I117" s="22" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="K117" s="22" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="M117" s="22" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="O117" s="22" t="n">
-        <v>-4.691</v>
-      </c>
-      <c r="P117" s="22" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="Q117" s="22" t="n">
-        <v>-20.209</v>
-      </c>
-      <c r="R117" s="22" t="n">
-        <v>-10.278</v>
-      </c>
-      <c r="S117" s="22" t="n">
-        <v>2.863</v>
-      </c>
-      <c r="T117" s="22" t="n">
-        <v>-7.942</v>
-      </c>
-      <c r="U117" s="22" t="n">
-        <v>-25.035</v>
-      </c>
-      <c r="V117" s="22" t="n">
-        <v>-27.436</v>
-      </c>
-      <c r="W117" s="22" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="X117" s="22" t="n">
-        <v>-0.382</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>임원 퇴직위로 충당금 증감</t>
-        </is>
-      </c>
-      <c r="O118" s="22" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="P118" s="22" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="Q118" s="22" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="R118" s="22" t="n">
-        <v>-9.166</v>
-      </c>
-      <c r="S118" s="22" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="T118" s="22" t="n">
-        <v>-0.494</v>
-      </c>
-      <c r="U118" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C119" s="22" t="n">
-        <v>9.351000000000001</v>
-      </c>
-      <c r="E119" s="22" t="n">
-        <v>57.508</v>
-      </c>
-      <c r="G119" s="22" t="n">
-        <v>29.884</v>
-      </c>
-      <c r="I119" s="22" t="n">
-        <v>55.182</v>
-      </c>
-      <c r="K119" s="22" t="n">
-        <v>-56.371</v>
-      </c>
-      <c r="M119" s="22" t="n">
-        <v>-38.877</v>
-      </c>
-      <c r="O119" s="22" t="n">
-        <v>-23.513</v>
-      </c>
-      <c r="P119" s="22" t="n">
-        <v>14.866</v>
-      </c>
-      <c r="Q119" s="22" t="n">
-        <v>44.022</v>
-      </c>
-      <c r="R119" s="22" t="n">
-        <v>-37.712</v>
-      </c>
-      <c r="S119" s="22" t="n">
-        <v>4.318</v>
-      </c>
-      <c r="T119" s="22" t="n">
-        <v>65.502</v>
-      </c>
-      <c r="U119" s="22" t="n">
-        <v>33.989</v>
-      </c>
-      <c r="V119" s="22" t="n">
-        <v>57.508</v>
-      </c>
-      <c r="W119" s="22" t="n">
-        <v>55.182</v>
-      </c>
-      <c r="X119" s="22" t="n">
-        <v>-38.877</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>임원 상여충당금 증감</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="C120" s="22" t="n">
-        <v>-60.5</v>
+        <v>128.71</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>36.8</v>
+        <v>276.554</v>
       </c>
       <c r="G120" s="22" t="n">
-        <v>-97.3</v>
+        <v>133.257</v>
       </c>
       <c r="I120" s="22" t="n">
-        <v>7.6</v>
+        <v>282.322</v>
       </c>
       <c r="K120" s="22" t="n">
-        <v>-104.9</v>
+        <v>123.956</v>
       </c>
       <c r="M120" s="22" t="n">
-        <v>7.1</v>
+        <v>277.364</v>
       </c>
       <c r="O120" s="22" t="n">
-        <v>-17</v>
+        <v>174.903</v>
       </c>
       <c r="P120" s="22" t="n">
-        <v>-16</v>
+        <v>184.337</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>35</v>
+        <v>219.436</v>
       </c>
       <c r="R120" s="22" t="n">
-        <v>-1</v>
+        <v>257.033</v>
       </c>
       <c r="S120" s="22" t="n">
-        <v>-12</v>
+        <v>280.818</v>
       </c>
       <c r="T120" s="22" t="n">
-        <v>36</v>
+        <v>269.007</v>
       </c>
       <c r="U120" s="22" t="n">
-        <v>2.5</v>
+        <v>259.703</v>
       </c>
       <c r="V120" s="22" t="n">
-        <v>36.8</v>
+        <v>276.554</v>
       </c>
       <c r="W120" s="22" t="n">
-        <v>7.6</v>
+        <v>282.322</v>
       </c>
       <c r="X120" s="22" t="n">
-        <v>7.1</v>
+        <v>277.364</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>제품보증 충당금 증감</t>
+          <t>주식보상비용</t>
         </is>
       </c>
       <c r="C121" s="22" t="n">
-        <v>-0.039</v>
+        <v>16.059</v>
       </c>
       <c r="E121" s="22" t="n">
-        <v>0.709</v>
+        <v>31.956</v>
       </c>
       <c r="G121" s="22" t="n">
-        <v>1.967</v>
+        <v>14.471</v>
       </c>
       <c r="I121" s="22" t="n">
-        <v>3.247</v>
+        <v>27.517</v>
       </c>
       <c r="K121" s="22" t="n">
-        <v>1.469</v>
+        <v>13.509</v>
       </c>
       <c r="M121" s="22" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="O121" s="22" t="n">
-        <v>-6.696</v>
-      </c>
-      <c r="P121" s="22" t="n">
-        <v>4.991</v>
+        <v>27.482</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>5.156</v>
+        <v>0</v>
       </c>
       <c r="R121" s="22" t="n">
-        <v>-6.625</v>
+        <v>18.898</v>
       </c>
       <c r="S121" s="22" t="n">
-        <v>-1.098</v>
+        <v>25.197</v>
       </c>
       <c r="T121" s="22" t="n">
-        <v>0.15</v>
+        <v>27.446</v>
       </c>
       <c r="U121" s="22" t="n">
-        <v>-0.706</v>
+        <v>27.134</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>0.709</v>
+        <v>31.956</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>3.247</v>
+        <v>27.517</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>0.6840000000000001</v>
+        <v>27.482</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="C122" s="22" t="n">
-        <v>-69.25</v>
-      </c>
-      <c r="E122" s="22" t="n">
-        <v>-114.141</v>
-      </c>
-      <c r="G122" s="22" t="n">
-        <v>-71.145</v>
-      </c>
-      <c r="I122" s="22" t="n">
-        <v>-131.221</v>
-      </c>
-      <c r="K122" s="22" t="n">
-        <v>-100.932</v>
-      </c>
-      <c r="M122" s="22" t="n">
-        <v>-153.842</v>
+          <t>대손충당금 증감</t>
+        </is>
       </c>
       <c r="O122" s="22" t="n">
-        <v>-37.513</v>
+        <v>0</v>
       </c>
       <c r="P122" s="22" t="n">
-        <v>-39.047</v>
+        <v>1.606</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>-49.606</v>
+        <v>0</v>
       </c>
       <c r="R122" s="22" t="n">
-        <v>-50.322</v>
+        <v>-1.575</v>
       </c>
       <c r="S122" s="22" t="n">
-        <v>-54.249</v>
-      </c>
-      <c r="T122" s="22" t="n">
-        <v>-67.372</v>
-      </c>
-      <c r="U122" s="22" t="n">
-        <v>-106.629</v>
-      </c>
-      <c r="V122" s="22" t="n">
-        <v>-114.141</v>
-      </c>
-      <c r="W122" s="22" t="n">
-        <v>-131.221</v>
-      </c>
-      <c r="X122" s="22" t="n">
-        <v>-153.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C123" s="22" t="n">
-        <v>2.018</v>
+          <t>퇴직급여자산 증감</t>
+        </is>
       </c>
       <c r="E123" s="22" t="n">
-        <v>4.041</v>
+        <v>0</v>
       </c>
       <c r="G123" s="22" t="n">
-        <v>2.264</v>
+        <v>0</v>
       </c>
       <c r="I123" s="22" t="n">
-        <v>4.534</v>
+        <v>-36.368</v>
       </c>
       <c r="K123" s="22" t="n">
-        <v>3.386</v>
+        <v>-22.237</v>
       </c>
       <c r="M123" s="22" t="n">
-        <v>6.782</v>
-      </c>
-      <c r="O123" s="22" t="n">
-        <v>15.479</v>
-      </c>
-      <c r="P123" s="22" t="n">
-        <v>16.212</v>
-      </c>
-      <c r="Q123" s="22" t="n">
-        <v>19.207</v>
-      </c>
-      <c r="R123" s="22" t="n">
-        <v>17.62</v>
-      </c>
-      <c r="S123" s="22" t="n">
-        <v>18.543</v>
-      </c>
-      <c r="T123" s="22" t="n">
-        <v>2.719</v>
-      </c>
-      <c r="U123" s="22" t="n">
-        <v>3.024</v>
+        <v>-43.593</v>
       </c>
       <c r="V123" s="22" t="n">
-        <v>4.041</v>
+        <v>0</v>
       </c>
       <c r="W123" s="22" t="n">
-        <v>4.534</v>
+        <v>-36.368</v>
       </c>
       <c r="X123" s="22" t="n">
-        <v>6.782</v>
+        <v>-43.593</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>Dismantlement Expenses Ope CF</t>
-        </is>
+          <t>퇴직급여부채 증감</t>
+        </is>
+      </c>
+      <c r="C124" s="22" t="n">
+        <v>-13.743</v>
+      </c>
+      <c r="E124" s="22" t="n">
+        <v>-27.436</v>
+      </c>
+      <c r="G124" s="22" t="n">
+        <v>-19.118</v>
+      </c>
+      <c r="I124" s="22" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="K124" s="22" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="M124" s="22" t="n">
+        <v>-0.382</v>
       </c>
       <c r="O124" s="22" t="n">
-        <v>0</v>
+        <v>-4.691</v>
       </c>
       <c r="P124" s="22" t="n">
-        <v>22.306</v>
+        <v>0.161</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>8.532999999999999</v>
+        <v>-20.209</v>
       </c>
       <c r="R124" s="22" t="n">
-        <v>0</v>
+        <v>-10.278</v>
+      </c>
+      <c r="S124" s="22" t="n">
+        <v>2.863</v>
+      </c>
+      <c r="T124" s="22" t="n">
+        <v>-7.942</v>
+      </c>
+      <c r="U124" s="22" t="n">
+        <v>-25.035</v>
+      </c>
+      <c r="V124" s="22" t="n">
+        <v>-27.436</v>
+      </c>
+      <c r="W124" s="22" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="X124" s="22" t="n">
+        <v>-0.382</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>유가증권 매각손익</t>
+          <t>임원 퇴직위로 충당금 증감</t>
         </is>
       </c>
       <c r="O125" s="22" t="n">
-        <v>-0.304</v>
+        <v>0.32</v>
       </c>
       <c r="P125" s="22" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q125" s="22" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="R125" s="22" t="n">
+        <v>-9.166</v>
+      </c>
+      <c r="S125" s="22" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="T125" s="22" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="U125" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>보험해약 손익</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C126" s="22" t="n">
+        <v>9.351000000000001</v>
+      </c>
+      <c r="E126" s="22" t="n">
+        <v>57.508</v>
+      </c>
+      <c r="G126" s="22" t="n">
+        <v>29.884</v>
+      </c>
+      <c r="I126" s="22" t="n">
+        <v>55.182</v>
+      </c>
+      <c r="K126" s="22" t="n">
+        <v>-56.371</v>
+      </c>
+      <c r="M126" s="22" t="n">
+        <v>-38.877</v>
+      </c>
+      <c r="O126" s="22" t="n">
+        <v>-23.513</v>
+      </c>
+      <c r="P126" s="22" t="n">
+        <v>14.866</v>
+      </c>
+      <c r="Q126" s="22" t="n">
+        <v>44.022</v>
       </c>
       <c r="R126" s="22" t="n">
-        <v>0</v>
+        <v>-37.712</v>
       </c>
       <c r="S126" s="22" t="n">
-        <v>3.879</v>
+        <v>4.318</v>
       </c>
       <c r="T126" s="22" t="n">
-        <v>0</v>
+        <v>65.502</v>
+      </c>
+      <c r="U126" s="22" t="n">
+        <v>33.989</v>
+      </c>
+      <c r="V126" s="22" t="n">
+        <v>57.508</v>
+      </c>
+      <c r="W126" s="22" t="n">
+        <v>55.182</v>
+      </c>
+      <c r="X126" s="22" t="n">
+        <v>-38.877</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
+          <t>임원 상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C127" s="22" t="n">
+        <v>-60.5</v>
       </c>
       <c r="E127" s="22" t="n">
-        <v>0</v>
+        <v>36.8</v>
+      </c>
+      <c r="G127" s="22" t="n">
+        <v>-97.3</v>
+      </c>
+      <c r="I127" s="22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K127" s="22" t="n">
+        <v>-104.9</v>
+      </c>
+      <c r="M127" s="22" t="n">
+        <v>7.1</v>
       </c>
       <c r="O127" s="22" t="n">
-        <v>-85.29300000000001</v>
+        <v>-17</v>
       </c>
       <c r="P127" s="22" t="n">
-        <v>-3.576</v>
+        <v>-16</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R127" s="22" t="n">
-        <v>-38.549</v>
+        <v>-1</v>
       </c>
       <c r="S127" s="22" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="T127" s="22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>-15.525</v>
+        <v>2.5</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>0</v>
+        <v>36.8</v>
+      </c>
+      <c r="W127" s="22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="X127" s="22" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>제품보증 충당금 증감</t>
         </is>
       </c>
       <c r="C128" s="22" t="n">
-        <v>258.777</v>
+        <v>-0.039</v>
       </c>
       <c r="E128" s="22" t="n">
-        <v>-795.599</v>
+        <v>0.709</v>
       </c>
       <c r="G128" s="22" t="n">
-        <v>470.603</v>
+        <v>1.967</v>
       </c>
       <c r="I128" s="22" t="n">
-        <v>51.543</v>
+        <v>3.247</v>
       </c>
       <c r="K128" s="22" t="n">
-        <v>568.745</v>
+        <v>1.469</v>
       </c>
       <c r="M128" s="22" t="n">
-        <v>61.156</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="O128" s="22" t="n">
-        <v>50.628</v>
+        <v>-6.696</v>
       </c>
       <c r="P128" s="22" t="n">
-        <v>-205.149</v>
+        <v>4.991</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>-121.472</v>
+        <v>5.156</v>
       </c>
       <c r="R128" s="22" t="n">
-        <v>-27.375</v>
+        <v>-6.625</v>
       </c>
       <c r="S128" s="22" t="n">
-        <v>664.168</v>
+        <v>-1.098</v>
       </c>
       <c r="T128" s="22" t="n">
-        <v>-223.047</v>
+        <v>0.15</v>
       </c>
       <c r="U128" s="22" t="n">
-        <v>-101.639</v>
+        <v>-0.706</v>
       </c>
       <c r="V128" s="22" t="n">
-        <v>-795.599</v>
+        <v>0.709</v>
       </c>
       <c r="W128" s="22" t="n">
-        <v>51.543</v>
+        <v>3.247</v>
       </c>
       <c r="X128" s="22" t="n">
-        <v>61.156</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="C129" s="22" t="n">
-        <v>-167.626</v>
+        <v>-69.25</v>
       </c>
       <c r="E129" s="22" t="n">
-        <v>509.726</v>
+        <v>-114.141</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>-237.124</v>
+        <v>-71.145</v>
       </c>
       <c r="I129" s="22" t="n">
-        <v>-261.343</v>
+        <v>-131.221</v>
       </c>
       <c r="K129" s="22" t="n">
-        <v>-239.731</v>
+        <v>-100.932</v>
       </c>
       <c r="M129" s="22" t="n">
-        <v>566.917</v>
+        <v>-153.842</v>
       </c>
       <c r="O129" s="22" t="n">
-        <v>112.495</v>
+        <v>-37.513</v>
       </c>
       <c r="P129" s="22" t="n">
-        <v>-292.073</v>
+        <v>-39.047</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>-297.876</v>
+        <v>-49.606</v>
       </c>
       <c r="R129" s="22" t="n">
-        <v>237.633</v>
+        <v>-50.322</v>
       </c>
       <c r="S129" s="22" t="n">
-        <v>-76.399</v>
+        <v>-54.249</v>
       </c>
       <c r="T129" s="22" t="n">
-        <v>-990.621</v>
+        <v>-67.372</v>
       </c>
       <c r="U129" s="22" t="n">
-        <v>-945.581</v>
+        <v>-106.629</v>
       </c>
       <c r="V129" s="22" t="n">
-        <v>509.726</v>
+        <v>-114.141</v>
       </c>
       <c r="W129" s="22" t="n">
-        <v>-261.343</v>
+        <v>-131.221</v>
       </c>
       <c r="X129" s="22" t="n">
-        <v>566.917</v>
+        <v>-153.842</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
-        <v>-296.923</v>
+        <v>2.018</v>
       </c>
       <c r="E130" s="22" t="n">
-        <v>-482.768</v>
+        <v>4.041</v>
       </c>
       <c r="G130" s="22" t="n">
-        <v>272.255</v>
+        <v>2.264</v>
       </c>
       <c r="I130" s="22" t="n">
-        <v>371.793</v>
+        <v>4.534</v>
       </c>
       <c r="K130" s="22" t="n">
-        <v>-226.571</v>
+        <v>3.386</v>
       </c>
       <c r="M130" s="22" t="n">
-        <v>-133.386</v>
+        <v>6.782</v>
       </c>
       <c r="O130" s="22" t="n">
-        <v>-115.9</v>
+        <v>15.479</v>
       </c>
       <c r="P130" s="22" t="n">
-        <v>192.206</v>
+        <v>16.212</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>42.011</v>
+        <v>19.207</v>
       </c>
       <c r="R130" s="22" t="n">
-        <v>-165.077</v>
+        <v>17.62</v>
       </c>
       <c r="S130" s="22" t="n">
-        <v>-83.471</v>
+        <v>18.543</v>
       </c>
       <c r="T130" s="22" t="n">
-        <v>311.566</v>
+        <v>2.719</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>111.965</v>
+        <v>3.024</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>-482.768</v>
+        <v>4.041</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>371.793</v>
+        <v>4.534</v>
       </c>
       <c r="X130" s="22" t="n">
-        <v>-133.386</v>
+        <v>6.782</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Insurance Funds Ope CF</t>
-        </is>
-      </c>
-      <c r="C131" s="22" t="n">
-        <v>-17.919</v>
-      </c>
-      <c r="E131" s="22" t="n">
-        <v>-36.852</v>
-      </c>
-      <c r="G131" s="22" t="n">
-        <v>-19.021</v>
-      </c>
-      <c r="I131" s="22" t="n">
-        <v>-38.042</v>
-      </c>
-      <c r="K131" s="22" t="n">
-        <v>19.885</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>4.063</v>
+          <t>Dismantlement Expenses Ope CF</t>
+        </is>
       </c>
       <c r="O131" s="22" t="n">
-        <v>-40.458</v>
+        <v>0</v>
       </c>
       <c r="P131" s="22" t="n">
-        <v>67.254</v>
+        <v>22.306</v>
       </c>
       <c r="Q131" s="22" t="n">
-        <v>-33.085</v>
+        <v>8.532999999999999</v>
       </c>
       <c r="R131" s="22" t="n">
-        <v>-33.085</v>
-      </c>
-      <c r="S131" s="22" t="n">
-        <v>13.038</v>
-      </c>
-      <c r="T131" s="22" t="n">
-        <v>-32.664</v>
-      </c>
-      <c r="U131" s="22" t="n">
-        <v>-34.17</v>
-      </c>
-      <c r="V131" s="22" t="n">
-        <v>-36.852</v>
-      </c>
-      <c r="W131" s="22" t="n">
-        <v>-38.042</v>
-      </c>
-      <c r="X131" s="22" t="n">
-        <v>4.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="C132" s="22" t="n">
-        <v>-17.86</v>
-      </c>
-      <c r="E132" s="22" t="n">
-        <v>68.008</v>
-      </c>
-      <c r="G132" s="22" t="n">
-        <v>-132.524</v>
-      </c>
-      <c r="I132" s="22" t="n">
-        <v>-67.87</v>
-      </c>
-      <c r="K132" s="22" t="n">
-        <v>-55.137</v>
-      </c>
-      <c r="M132" s="22" t="n">
-        <v>9.798</v>
+          <t>유가증권 매각손익</t>
+        </is>
+      </c>
+      <c r="O132" s="22" t="n">
+        <v>-0.304</v>
       </c>
       <c r="P132" s="22" t="n">
-        <v>-35.334</v>
-      </c>
-      <c r="Q132" s="22" t="n">
-        <v>22.815</v>
-      </c>
-      <c r="R132" s="22" t="n">
-        <v>5.716</v>
-      </c>
-      <c r="S132" s="22" t="n">
-        <v>-26.555</v>
-      </c>
-      <c r="T132" s="22" t="n">
-        <v>-51.169</v>
-      </c>
-      <c r="U132" s="22" t="n">
-        <v>105.38</v>
-      </c>
-      <c r="V132" s="22" t="n">
-        <v>68.008</v>
-      </c>
-      <c r="W132" s="22" t="n">
-        <v>-67.87</v>
-      </c>
-      <c r="X132" s="22" t="n">
-        <v>9.798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>미수 소비세 증감</t>
-        </is>
-      </c>
-      <c r="C133" s="22" t="n">
-        <v>-9.295999999999999</v>
-      </c>
-      <c r="E133" s="22" t="n">
-        <v>45.787</v>
-      </c>
-      <c r="G133" s="22" t="n">
-        <v>36.441</v>
-      </c>
-      <c r="I133" s="22" t="n">
-        <v>14.468</v>
-      </c>
-      <c r="K133" s="22" t="n">
-        <v>-15.527</v>
-      </c>
-      <c r="M133" s="22" t="n">
-        <v>32.167</v>
+          <t>보험해약 손익</t>
+        </is>
+      </c>
+      <c r="R133" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="S133" s="22" t="n">
+        <v>3.879</v>
+      </c>
+      <c r="T133" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="T133" s="22" t="n">
-        <v>-28.702</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>-69.69</v>
-      </c>
-      <c r="V133" s="22" t="n">
-        <v>45.787</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>14.468</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>32.167</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Temporary Payments Ope CF</t>
-        </is>
-      </c>
-      <c r="C134" s="22" t="n">
-        <v>-100.367</v>
-      </c>
-      <c r="G134" s="22" t="n">
-        <v>33.166</v>
-      </c>
-      <c r="K134" s="22" t="n">
-        <v>3.069</v>
+          <t>투자유가증권 매각손익</t>
+        </is>
+      </c>
+      <c r="E134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="22" t="n">
+        <v>-85.29300000000001</v>
+      </c>
+      <c r="P134" s="22" t="n">
+        <v>-3.576</v>
+      </c>
+      <c r="Q134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="22" t="n">
+        <v>-38.549</v>
+      </c>
+      <c r="S134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" s="22" t="n">
+        <v>-15.525</v>
+      </c>
+      <c r="V134" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="C135" s="22" t="n">
-        <v>22.506</v>
+        <v>258.777</v>
       </c>
       <c r="E135" s="22" t="n">
-        <v>61.036</v>
+        <v>-795.599</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>-76.66</v>
+        <v>470.603</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>-11.152</v>
+        <v>51.543</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>-17.785</v>
+        <v>568.745</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>48.359</v>
+        <v>61.156</v>
+      </c>
+      <c r="O135" s="22" t="n">
+        <v>50.628</v>
+      </c>
+      <c r="P135" s="22" t="n">
+        <v>-205.149</v>
       </c>
       <c r="Q135" s="22" t="n">
-        <v>2.453</v>
+        <v>-121.472</v>
       </c>
       <c r="R135" s="22" t="n">
-        <v>-18.474</v>
+        <v>-27.375</v>
       </c>
       <c r="S135" s="22" t="n">
-        <v>-16.059</v>
+        <v>664.168</v>
       </c>
       <c r="T135" s="22" t="n">
-        <v>-50.122</v>
+        <v>-223.047</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>-30.752</v>
+        <v>-101.639</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>61.036</v>
+        <v>-795.599</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>-11.152</v>
+        <v>51.543</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>48.359</v>
+        <v>61.156</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>예수금 증감</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="C136" s="22" t="n">
-        <v>-276.449</v>
+        <v>-167.626</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>-236.495</v>
+        <v>509.726</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>-70.69</v>
+        <v>-237.124</v>
       </c>
       <c r="I136" s="22" t="n">
-        <v>-16.687</v>
+        <v>-261.343</v>
       </c>
       <c r="K136" s="22" t="n">
-        <v>-45.492</v>
+        <v>-239.731</v>
       </c>
       <c r="M136" s="22" t="n">
-        <v>6.23</v>
+        <v>566.917</v>
+      </c>
+      <c r="O136" s="22" t="n">
+        <v>112.495</v>
+      </c>
+      <c r="P136" s="22" t="n">
+        <v>-292.073</v>
+      </c>
+      <c r="Q136" s="22" t="n">
+        <v>-297.876</v>
+      </c>
+      <c r="R136" s="22" t="n">
+        <v>237.633</v>
+      </c>
+      <c r="S136" s="22" t="n">
+        <v>-76.399</v>
       </c>
       <c r="T136" s="22" t="n">
-        <v>25.253</v>
+        <v>-990.621</v>
       </c>
       <c r="U136" s="22" t="n">
-        <v>257.986</v>
+        <v>-945.581</v>
       </c>
       <c r="V136" s="22" t="n">
-        <v>-236.495</v>
+        <v>509.726</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>-16.687</v>
+        <v>-261.343</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>6.23</v>
+        <v>566.917</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="C137" s="22" t="n">
-        <v>-13.54</v>
+        <v>-296.923</v>
       </c>
       <c r="E137" s="22" t="n">
-        <v>-23.355</v>
+        <v>-482.768</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>-11.044</v>
+        <v>272.255</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>44.479</v>
+        <v>371.793</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>-7.256</v>
+        <v>-226.571</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>-3.273</v>
+        <v>-133.386</v>
       </c>
       <c r="O137" s="22" t="n">
-        <v>2.229</v>
+        <v>-115.9</v>
       </c>
       <c r="P137" s="22" t="n">
-        <v>51.354</v>
+        <v>192.206</v>
       </c>
       <c r="Q137" s="22" t="n">
-        <v>24.643</v>
+        <v>42.011</v>
       </c>
       <c r="R137" s="22" t="n">
-        <v>-8.071</v>
+        <v>-165.077</v>
       </c>
       <c r="S137" s="22" t="n">
-        <v>8.538</v>
+        <v>-83.471</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>-21.636</v>
+        <v>311.566</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-12.658</v>
+        <v>111.965</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>-23.355</v>
+        <v>-482.768</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>44.479</v>
+        <v>371.793</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>-3.273</v>
+        <v>-133.386</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>Decrease Increase In Insurance Funds Ope CF</t>
         </is>
       </c>
       <c r="C138" s="22" t="n">
-        <v>201.919</v>
+        <v>-17.919</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>1294.892</v>
+        <v>-36.852</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>1176.234</v>
+        <v>-19.021</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>2423.539</v>
+        <v>-38.042</v>
       </c>
       <c r="K138" s="22" t="n">
-        <v>802.099</v>
+        <v>19.885</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>2945.46</v>
+        <v>4.063</v>
       </c>
       <c r="O138" s="22" t="n">
-        <v>578.051</v>
+        <v>-40.458</v>
       </c>
       <c r="P138" s="22" t="n">
-        <v>432.545</v>
+        <v>67.254</v>
       </c>
       <c r="Q138" s="22" t="n">
-        <v>576.726</v>
+        <v>-33.085</v>
       </c>
       <c r="R138" s="22" t="n">
-        <v>828.8</v>
+        <v>-33.085</v>
       </c>
       <c r="S138" s="22" t="n">
-        <v>1212.044</v>
+        <v>13.038</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>351.687</v>
+        <v>-32.664</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>1003.516</v>
+        <v>-34.17</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>1294.892</v>
+        <v>-36.852</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>2423.539</v>
+        <v>-38.042</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>2945.46</v>
+        <v>4.063</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>미지급 소비세 증감</t>
         </is>
       </c>
       <c r="C139" s="22" t="n">
-        <v>69.31100000000001</v>
+        <v>-17.86</v>
       </c>
       <c r="E139" s="22" t="n">
-        <v>114.201</v>
+        <v>68.008</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>71.151</v>
+        <v>-132.524</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>131.106</v>
+        <v>-67.87</v>
       </c>
       <c r="K139" s="22" t="n">
-        <v>99.54300000000001</v>
+        <v>-55.137</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>150.373</v>
-      </c>
-      <c r="O139" s="22" t="n">
-        <v>37.941</v>
+        <v>9.798</v>
       </c>
       <c r="P139" s="22" t="n">
-        <v>39.027</v>
+        <v>-35.334</v>
       </c>
       <c r="Q139" s="22" t="n">
-        <v>49.378</v>
+        <v>22.815</v>
       </c>
       <c r="R139" s="22" t="n">
-        <v>50.272</v>
+        <v>5.716</v>
       </c>
       <c r="S139" s="22" t="n">
-        <v>54.3</v>
+        <v>-26.555</v>
       </c>
       <c r="T139" s="22" t="n">
-        <v>67.398</v>
+        <v>-51.169</v>
       </c>
       <c r="U139" s="22" t="n">
-        <v>107.594</v>
+        <v>105.38</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>114.201</v>
+        <v>68.008</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>131.106</v>
+        <v>-67.87</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>150.373</v>
+        <v>9.798</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>미수 소비세 증감</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
-        <v>-3.024</v>
+        <v>-9.295999999999999</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-3.024</v>
+        <v>45.787</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>-4.041</v>
+        <v>36.441</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>-4.042</v>
+        <v>14.468</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>-4.533</v>
+        <v>-15.527</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>-4.534</v>
-      </c>
-      <c r="O140" s="22" t="n">
-        <v>-15.984</v>
-      </c>
-      <c r="P140" s="22" t="n">
-        <v>-16.185</v>
-      </c>
-      <c r="Q140" s="22" t="n">
-        <v>-19.005</v>
-      </c>
-      <c r="R140" s="22" t="n">
-        <v>-17.59</v>
+        <v>32.167</v>
       </c>
       <c r="S140" s="22" t="n">
-        <v>-18.663</v>
+        <v>0</v>
       </c>
       <c r="T140" s="22" t="n">
-        <v>-2.56</v>
+        <v>-28.702</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>-2.719</v>
+        <v>-69.69</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-3.024</v>
+        <v>45.787</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>-4.042</v>
+        <v>14.468</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>-4.534</v>
+        <v>32.167</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>Decrease Increase In Temporary Payments Ope CF</t>
         </is>
       </c>
       <c r="C141" s="22" t="n">
-        <v>-429.263</v>
-      </c>
-      <c r="E141" s="22" t="n">
-        <v>-691.247</v>
+        <v>-100.367</v>
       </c>
       <c r="G141" s="22" t="n">
-        <v>-261.373</v>
-      </c>
-      <c r="I141" s="22" t="n">
-        <v>-454.309</v>
+        <v>33.166</v>
       </c>
       <c r="K141" s="22" t="n">
-        <v>-568.989</v>
-      </c>
-      <c r="M141" s="22" t="n">
-        <v>-807.658</v>
-      </c>
-      <c r="O141" s="22" t="n">
-        <v>-295.223</v>
-      </c>
-      <c r="P141" s="22" t="n">
-        <v>-198.12</v>
-      </c>
-      <c r="Q141" s="22" t="n">
-        <v>-105.504</v>
-      </c>
-      <c r="R141" s="22" t="n">
-        <v>-92.215</v>
-      </c>
-      <c r="S141" s="22" t="n">
-        <v>-177.099</v>
-      </c>
-      <c r="T141" s="22" t="n">
-        <v>-352.831</v>
-      </c>
-      <c r="U141" s="22" t="n">
-        <v>-1070.797</v>
-      </c>
-      <c r="V141" s="22" t="n">
-        <v>-691.247</v>
-      </c>
-      <c r="W141" s="22" t="n">
-        <v>-454.309</v>
-      </c>
-      <c r="X141" s="22" t="n">
-        <v>-807.658</v>
+        <v>3.069</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>미지급금 증감</t>
         </is>
       </c>
       <c r="C142" s="22" t="n">
-        <v>517.547</v>
+        <v>22.506</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>517.547</v>
+        <v>61.036</v>
       </c>
       <c r="G142" s="22" t="n">
-        <v>49.263</v>
+        <v>-76.66</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>49.253</v>
+        <v>-11.152</v>
       </c>
       <c r="K142" s="22" t="n">
-        <v>0</v>
+        <v>-17.785</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" s="22" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="P142" s="22" t="n">
-        <v>0</v>
+        <v>48.359</v>
+      </c>
+      <c r="Q142" s="22" t="n">
+        <v>2.453</v>
+      </c>
+      <c r="R142" s="22" t="n">
+        <v>-18.474</v>
+      </c>
+      <c r="S142" s="22" t="n">
+        <v>-16.059</v>
+      </c>
+      <c r="T142" s="22" t="n">
+        <v>-50.122</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>0</v>
+        <v>-30.752</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>517.547</v>
+        <v>61.036</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>49.253</v>
+        <v>-11.152</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>0</v>
+        <v>48.359</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C143" s="12" t="n">
-        <v>356.49</v>
-      </c>
-      <c r="E143" s="12" t="n">
-        <v>1232.369</v>
-      </c>
-      <c r="G143" s="12" t="n">
-        <v>1031.234</v>
-      </c>
-      <c r="I143" s="12" t="n">
-        <v>2145.548</v>
-      </c>
-      <c r="K143" s="12" t="n">
-        <v>328.12</v>
-      </c>
-      <c r="M143" s="12" t="n">
-        <v>2283.641</v>
-      </c>
-      <c r="O143" s="12" t="n">
-        <v>326.985</v>
-      </c>
-      <c r="P143" s="12" t="n">
-        <v>257.267</v>
-      </c>
-      <c r="Q143" s="12" t="n">
-        <v>501.594</v>
-      </c>
-      <c r="R143" s="12" t="n">
-        <v>769.2670000000001</v>
-      </c>
-      <c r="S143" s="12" t="n">
-        <v>1070.581</v>
-      </c>
-      <c r="T143" s="12" t="n">
-        <v>63.693</v>
-      </c>
-      <c r="U143" s="12" t="n">
-        <v>37.593</v>
-      </c>
-      <c r="V143" s="12" t="n">
-        <v>1232.369</v>
-      </c>
-      <c r="W143" s="12" t="n">
-        <v>2145.548</v>
-      </c>
-      <c r="X143" s="12" t="n">
-        <v>2283.641</v>
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>예수금 증감</t>
+        </is>
+      </c>
+      <c r="C143" s="22" t="n">
+        <v>-276.449</v>
+      </c>
+      <c r="E143" s="22" t="n">
+        <v>-236.495</v>
+      </c>
+      <c r="G143" s="22" t="n">
+        <v>-70.69</v>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>-16.687</v>
+      </c>
+      <c r="K143" s="22" t="n">
+        <v>-45.492</v>
+      </c>
+      <c r="M143" s="22" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>25.253</v>
+      </c>
+      <c r="U143" s="22" t="n">
+        <v>257.986</v>
+      </c>
+      <c r="V143" s="22" t="n">
+        <v>-236.495</v>
+      </c>
+      <c r="W143" s="22" t="n">
+        <v>-16.687</v>
+      </c>
+      <c r="X143" s="22" t="n">
+        <v>6.23</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>유가증권 매각·상환 수입</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C144" s="22" t="n">
-        <v>50</v>
+        <v>-13.54</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>50</v>
+        <v>-23.355</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>0</v>
+        <v>-11.044</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>50</v>
+        <v>44.479</v>
+      </c>
+      <c r="K144" s="22" t="n">
+        <v>-7.256</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>0</v>
+        <v>-3.273</v>
+      </c>
+      <c r="O144" s="22" t="n">
+        <v>2.229</v>
+      </c>
+      <c r="P144" s="22" t="n">
+        <v>51.354</v>
+      </c>
+      <c r="Q144" s="22" t="n">
+        <v>24.643</v>
+      </c>
+      <c r="R144" s="22" t="n">
+        <v>-8.071</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>0</v>
+        <v>8.538</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>40</v>
+        <v>-21.636</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>50</v>
+        <v>-12.658</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>50</v>
+        <v>-23.355</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>50</v>
+        <v>44.479</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>0</v>
+        <v>-3.273</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>정기예금 순증감</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C145" s="22" t="n">
+        <v>201.919</v>
       </c>
       <c r="E145" s="22" t="n">
-        <v>-0</v>
+        <v>1294.892</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>-0</v>
+        <v>1176.234</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>-0</v>
+        <v>2423.539</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>-146.904</v>
+        <v>802.099</v>
       </c>
       <c r="M145" s="22" t="n">
-        <v>-148.541</v>
+        <v>2945.46</v>
       </c>
       <c r="O145" s="22" t="n">
-        <v>64.398</v>
+        <v>578.051</v>
       </c>
       <c r="P145" s="22" t="n">
-        <v>33.478</v>
+        <v>432.545</v>
       </c>
       <c r="Q145" s="22" t="n">
-        <v>-16.54</v>
+        <v>576.726</v>
       </c>
       <c r="R145" s="22" t="n">
-        <v>-0</v>
+        <v>828.8</v>
       </c>
       <c r="S145" s="22" t="n">
-        <v>-0</v>
+        <v>1212.044</v>
       </c>
       <c r="T145" s="22" t="n">
-        <v>0</v>
+        <v>351.687</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>78.999</v>
+        <v>1003.516</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>-0</v>
+        <v>1294.892</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>-0</v>
+        <v>2423.539</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>-148.541</v>
+        <v>2945.46</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="C146" s="22" t="n">
-        <v>-127.677</v>
+        <v>69.31100000000001</v>
       </c>
       <c r="E146" s="22" t="n">
-        <v>-272.357</v>
+        <v>114.201</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>-124.697</v>
+        <v>71.151</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>-232.535</v>
+        <v>131.106</v>
       </c>
       <c r="K146" s="22" t="n">
-        <v>-79.074</v>
+        <v>99.54300000000001</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>-406.931</v>
+        <v>150.373</v>
       </c>
       <c r="O146" s="22" t="n">
-        <v>-132.584</v>
+        <v>37.941</v>
       </c>
       <c r="P146" s="22" t="n">
-        <v>-269.389</v>
+        <v>39.027</v>
       </c>
       <c r="Q146" s="22" t="n">
-        <v>-383.118</v>
+        <v>49.378</v>
       </c>
       <c r="R146" s="22" t="n">
-        <v>-236.474</v>
+        <v>50.272</v>
       </c>
       <c r="S146" s="22" t="n">
-        <v>-178.877</v>
+        <v>54.3</v>
       </c>
       <c r="T146" s="22" t="n">
-        <v>-136.31</v>
+        <v>67.398</v>
       </c>
       <c r="U146" s="22" t="n">
-        <v>-144.137</v>
+        <v>107.594</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>-272.357</v>
+        <v>114.201</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>-232.535</v>
+        <v>131.106</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>-406.931</v>
+        <v>150.373</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>Payments For Dismantling Of Property Plant And Equipment Inv CF</t>
-        </is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="C147" s="22" t="n">
+        <v>-3.024</v>
+      </c>
+      <c r="E147" s="22" t="n">
+        <v>-3.024</v>
+      </c>
+      <c r="G147" s="22" t="n">
+        <v>-4.041</v>
+      </c>
+      <c r="I147" s="22" t="n">
+        <v>-4.042</v>
+      </c>
+      <c r="K147" s="22" t="n">
+        <v>-4.533</v>
+      </c>
+      <c r="M147" s="22" t="n">
+        <v>-4.534</v>
       </c>
       <c r="O147" s="22" t="n">
-        <v>0</v>
+        <v>-15.984</v>
       </c>
       <c r="P147" s="22" t="n">
-        <v>-16.868</v>
+        <v>-16.185</v>
       </c>
       <c r="Q147" s="22" t="n">
-        <v>-13.972</v>
+        <v>-19.005</v>
       </c>
       <c r="R147" s="22" t="n">
-        <v>0</v>
+        <v>-17.59</v>
+      </c>
+      <c r="S147" s="22" t="n">
+        <v>-18.663</v>
+      </c>
+      <c r="T147" s="22" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="U147" s="22" t="n">
+        <v>-2.719</v>
+      </c>
+      <c r="V147" s="22" t="n">
+        <v>-3.024</v>
+      </c>
+      <c r="W147" s="22" t="n">
+        <v>-4.042</v>
+      </c>
+      <c r="X147" s="22" t="n">
+        <v>-4.534</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="C148" s="22" t="n">
-        <v>-25.826</v>
+        <v>-429.263</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-26.906</v>
+        <v>-691.247</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>-12.708</v>
+        <v>-261.373</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>-16.388</v>
+        <v>-454.309</v>
       </c>
       <c r="K148" s="22" t="n">
-        <v>-130.398</v>
+        <v>-568.989</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>-239.602</v>
+        <v>-807.658</v>
       </c>
       <c r="O148" s="22" t="n">
-        <v>-25.045</v>
+        <v>-295.223</v>
       </c>
       <c r="P148" s="22" t="n">
-        <v>-21.84</v>
+        <v>-198.12</v>
       </c>
       <c r="Q148" s="22" t="n">
-        <v>-66.908</v>
+        <v>-105.504</v>
       </c>
       <c r="R148" s="22" t="n">
-        <v>-57.656</v>
+        <v>-92.215</v>
       </c>
       <c r="S148" s="22" t="n">
-        <v>-31.894</v>
+        <v>-177.099</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>-13.307</v>
+        <v>-352.831</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>-17.803</v>
+        <v>-1070.797</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>-26.906</v>
+        <v>-691.247</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>-16.388</v>
+        <v>-454.309</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>-239.602</v>
+        <v>-807.658</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>법인세 환급</t>
         </is>
       </c>
       <c r="C149" s="22" t="n">
-        <v>-5.684</v>
+        <v>517.547</v>
       </c>
       <c r="E149" s="22" t="n">
-        <v>-10.308</v>
+        <v>517.547</v>
       </c>
       <c r="G149" s="22" t="n">
-        <v>-4.537</v>
+        <v>49.263</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>-11.433</v>
+        <v>49.253</v>
       </c>
       <c r="K149" s="22" t="n">
-        <v>-6.791</v>
+        <v>0</v>
       </c>
       <c r="M149" s="22" t="n">
-        <v>-112.871</v>
+        <v>0</v>
       </c>
       <c r="O149" s="22" t="n">
-        <v>-96.26600000000001</v>
+        <v>22.2</v>
       </c>
       <c r="P149" s="22" t="n">
-        <v>-106.394</v>
-      </c>
-      <c r="Q149" s="22" t="n">
-        <v>-57.282</v>
-      </c>
-      <c r="R149" s="22" t="n">
-        <v>-57.803</v>
-      </c>
-      <c r="S149" s="22" t="n">
-        <v>-88.417</v>
-      </c>
-      <c r="T149" s="22" t="n">
-        <v>-8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>-59.486</v>
+        <v>0</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>-10.308</v>
+        <v>517.547</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>-11.433</v>
+        <v>49.253</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>-112.871</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각·상환 수입</t>
-        </is>
-      </c>
-      <c r="E150" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" s="22" t="n">
-        <v>154.907</v>
-      </c>
-      <c r="P150" s="22" t="n">
-        <v>11.038</v>
-      </c>
-      <c r="Q150" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" s="22" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="S150" s="22" t="n">
-        <v>20.811</v>
-      </c>
-      <c r="T150" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" s="22" t="n">
-        <v>29.63</v>
-      </c>
-      <c r="V150" s="22" t="n">
-        <v>0</v>
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="n">
+        <v>356.49</v>
+      </c>
+      <c r="E150" s="12" t="n">
+        <v>1232.369</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>1031.234</v>
+      </c>
+      <c r="I150" s="12" t="n">
+        <v>2145.548</v>
+      </c>
+      <c r="K150" s="12" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="M150" s="12" t="n">
+        <v>2283.641</v>
+      </c>
+      <c r="O150" s="12" t="n">
+        <v>326.985</v>
+      </c>
+      <c r="P150" s="12" t="n">
+        <v>257.267</v>
+      </c>
+      <c r="Q150" s="12" t="n">
+        <v>501.594</v>
+      </c>
+      <c r="R150" s="12" t="n">
+        <v>769.2670000000001</v>
+      </c>
+      <c r="S150" s="12" t="n">
+        <v>1070.581</v>
+      </c>
+      <c r="T150" s="12" t="n">
+        <v>63.693</v>
+      </c>
+      <c r="U150" s="12" t="n">
+        <v>37.593</v>
+      </c>
+      <c r="V150" s="12" t="n">
+        <v>1232.369</v>
+      </c>
+      <c r="W150" s="12" t="n">
+        <v>2145.548</v>
+      </c>
+      <c r="X150" s="12" t="n">
+        <v>2283.641</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of More Investments In Subsidiaries Inv CF</t>
-        </is>
-      </c>
-      <c r="P151" s="22" t="n">
+          <t>유가증권 매각·상환 수입</t>
+        </is>
+      </c>
+      <c r="C151" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="E151" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="G151" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" s="22" t="n">
-        <v>-30.375</v>
-      </c>
-      <c r="R151" s="22" t="n">
+      <c r="I151" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="M151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="U151" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="V151" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="X151" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Memberships Inv CF</t>
+          <t>정기예금 순증감</t>
         </is>
       </c>
       <c r="E152" s="22" t="n">
-        <v>-7.421</v>
+        <v>-0</v>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>-0</v>
       </c>
       <c r="I152" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K152" s="22" t="n">
+        <v>-146.904</v>
+      </c>
+      <c r="M152" s="22" t="n">
+        <v>-148.541</v>
+      </c>
+      <c r="O152" s="22" t="n">
+        <v>64.398</v>
+      </c>
+      <c r="P152" s="22" t="n">
+        <v>33.478</v>
+      </c>
+      <c r="Q152" s="22" t="n">
+        <v>-16.54</v>
+      </c>
+      <c r="R152" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S152" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T152" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U152" s="22" t="n">
-        <v>0</v>
+        <v>78.999</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>-7.421</v>
+        <v>-0</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>-148.541</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C153" s="22" t="n">
-        <v>2.679</v>
+        <v>-127.677</v>
       </c>
       <c r="E153" s="22" t="n">
-        <v>2.108</v>
+        <v>-272.357</v>
       </c>
       <c r="G153" s="22" t="n">
-        <v>0.14</v>
+        <v>-124.697</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>-0.705</v>
+        <v>-232.535</v>
       </c>
       <c r="K153" s="22" t="n">
-        <v>0.625</v>
+        <v>-79.074</v>
       </c>
       <c r="M153" s="22" t="n">
-        <v>-0.86</v>
+        <v>-406.931</v>
       </c>
       <c r="O153" s="22" t="n">
-        <v>-0.476</v>
+        <v>-132.584</v>
       </c>
       <c r="P153" s="22" t="n">
-        <v>-5.472</v>
+        <v>-269.389</v>
       </c>
       <c r="Q153" s="22" t="n">
-        <v>0.605</v>
+        <v>-383.118</v>
       </c>
       <c r="R153" s="22" t="n">
-        <v>1.43</v>
+        <v>-236.474</v>
       </c>
       <c r="S153" s="22" t="n">
-        <v>0.639</v>
+        <v>-178.877</v>
       </c>
       <c r="T153" s="22" t="n">
-        <v>-1.27</v>
+        <v>-136.31</v>
       </c>
       <c r="U153" s="22" t="n">
-        <v>0.995</v>
+        <v>-144.137</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>2.108</v>
+        <v>-272.357</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>-0.705</v>
+        <v>-232.535</v>
       </c>
       <c r="X153" s="22" t="n">
-        <v>-0.86</v>
+        <v>-406.931</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C154" s="12" t="n">
-        <v>-106.509</v>
-      </c>
-      <c r="E154" s="12" t="n">
-        <v>-264.885</v>
-      </c>
-      <c r="G154" s="12" t="n">
-        <v>-141.804</v>
-      </c>
-      <c r="I154" s="12" t="n">
-        <v>-211.063</v>
-      </c>
-      <c r="K154" s="12" t="n">
-        <v>-362.543</v>
-      </c>
-      <c r="M154" s="12" t="n">
-        <v>-908.806</v>
-      </c>
-      <c r="O154" s="12" t="n">
-        <v>-35.065</v>
-      </c>
-      <c r="P154" s="12" t="n">
-        <v>-375.448</v>
-      </c>
-      <c r="Q154" s="12" t="n">
-        <v>-567.592</v>
-      </c>
-      <c r="R154" s="12" t="n">
-        <v>-307.865</v>
-      </c>
-      <c r="S154" s="12" t="n">
-        <v>-277.738</v>
-      </c>
-      <c r="T154" s="12" t="n">
-        <v>-119.259</v>
-      </c>
-      <c r="U154" s="12" t="n">
-        <v>-61.802</v>
-      </c>
-      <c r="V154" s="12" t="n">
-        <v>-264.885</v>
-      </c>
-      <c r="W154" s="12" t="n">
-        <v>-211.063</v>
-      </c>
-      <c r="X154" s="12" t="n">
-        <v>-908.806</v>
+      <c r="A154" s="20" t="inlineStr">
+        <is>
+          <t>Payments For Dismantling Of Property Plant And Equipment Inv CF</t>
+        </is>
+      </c>
+      <c r="O154" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="22" t="n">
+        <v>-16.868</v>
+      </c>
+      <c r="Q154" s="22" t="n">
+        <v>-13.972</v>
+      </c>
+      <c r="R154" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="C155" s="22" t="n">
+        <v>-25.826</v>
       </c>
       <c r="E155" s="22" t="n">
-        <v>-139.242</v>
+        <v>-26.906</v>
+      </c>
+      <c r="G155" s="22" t="n">
+        <v>-12.708</v>
       </c>
       <c r="I155" s="22" t="n">
-        <v>0</v>
+        <v>-16.388</v>
+      </c>
+      <c r="K155" s="22" t="n">
+        <v>-130.398</v>
+      </c>
+      <c r="M155" s="22" t="n">
+        <v>-239.602</v>
       </c>
       <c r="O155" s="22" t="n">
-        <v>-45.581</v>
+        <v>-25.045</v>
       </c>
       <c r="P155" s="22" t="n">
-        <v>-32.789</v>
+        <v>-21.84</v>
       </c>
       <c r="Q155" s="22" t="n">
-        <v>-70.048</v>
+        <v>-66.908</v>
       </c>
       <c r="R155" s="22" t="n">
-        <v>-0.04</v>
+        <v>-57.656</v>
       </c>
       <c r="S155" s="22" t="n">
-        <v>0</v>
+        <v>-31.894</v>
       </c>
       <c r="T155" s="22" t="n">
-        <v>-0.121</v>
+        <v>-13.307</v>
       </c>
       <c r="U155" s="22" t="n">
-        <v>0</v>
+        <v>-17.803</v>
       </c>
       <c r="V155" s="22" t="n">
-        <v>-139.242</v>
+        <v>-26.906</v>
       </c>
       <c r="W155" s="22" t="n">
-        <v>0</v>
+        <v>-16.388</v>
+      </c>
+      <c r="X155" s="22" t="n">
+        <v>-239.602</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
+          <t>투자유가증권 취득</t>
         </is>
       </c>
       <c r="C156" s="22" t="n">
-        <v>-2.258</v>
+        <v>-5.684</v>
       </c>
       <c r="E156" s="22" t="n">
-        <v>-4.449</v>
+        <v>-10.308</v>
       </c>
       <c r="G156" s="22" t="n">
-        <v>-1.533</v>
+        <v>-4.537</v>
       </c>
       <c r="I156" s="22" t="n">
-        <v>-4.308</v>
+        <v>-11.433</v>
       </c>
       <c r="K156" s="22" t="n">
-        <v>-2.329</v>
+        <v>-6.791</v>
       </c>
       <c r="M156" s="22" t="n">
-        <v>-4.405</v>
+        <v>-112.871</v>
       </c>
       <c r="O156" s="22" t="n">
-        <v>-4.058</v>
+        <v>-96.26600000000001</v>
       </c>
       <c r="P156" s="22" t="n">
-        <v>-2.833</v>
+        <v>-106.394</v>
       </c>
       <c r="Q156" s="22" t="n">
-        <v>-2.357</v>
+        <v>-57.282</v>
       </c>
       <c r="R156" s="22" t="n">
-        <v>-3.375</v>
+        <v>-57.803</v>
       </c>
       <c r="S156" s="22" t="n">
-        <v>-4.006</v>
+        <v>-88.417</v>
       </c>
       <c r="T156" s="22" t="n">
-        <v>-4.157</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="U156" s="22" t="n">
-        <v>-4.686</v>
+        <v>-59.486</v>
       </c>
       <c r="V156" s="22" t="n">
-        <v>-4.449</v>
+        <v>-10.308</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>-4.308</v>
+        <v>-11.433</v>
       </c>
       <c r="X156" s="22" t="n">
-        <v>-4.405</v>
+        <v>-112.871</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="C157" s="22" t="n">
-        <v>-317.362</v>
+          <t>투자유가증권 매각·상환 수입</t>
+        </is>
       </c>
       <c r="E157" s="22" t="n">
-        <v>-317.508</v>
-      </c>
-      <c r="G157" s="22" t="n">
-        <v>-386.044</v>
-      </c>
-      <c r="I157" s="22" t="n">
-        <v>-387.285</v>
-      </c>
-      <c r="K157" s="22" t="n">
-        <v>-437.26</v>
-      </c>
-      <c r="M157" s="22" t="n">
-        <v>-441.444</v>
+        <v>0</v>
       </c>
       <c r="O157" s="22" t="n">
-        <v>-185.517</v>
+        <v>154.907</v>
       </c>
       <c r="P157" s="22" t="n">
-        <v>-182.849</v>
+        <v>11.038</v>
       </c>
       <c r="Q157" s="22" t="n">
-        <v>-182.999</v>
+        <v>0</v>
       </c>
       <c r="R157" s="22" t="n">
-        <v>-189.799</v>
+        <v>42.64</v>
       </c>
       <c r="S157" s="22" t="n">
-        <v>-191.393</v>
+        <v>20.811</v>
       </c>
       <c r="T157" s="22" t="n">
-        <v>-166.072</v>
+        <v>0</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>-250.2</v>
+        <v>29.63</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>-317.508</v>
-      </c>
-      <c r="W157" s="22" t="n">
-        <v>-387.285</v>
-      </c>
-      <c r="X157" s="22" t="n">
-        <v>-441.444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C158" s="12" t="n">
-        <v>-319.621</v>
-      </c>
-      <c r="E158" s="12" t="n">
-        <v>-461.199</v>
-      </c>
-      <c r="G158" s="12" t="n">
-        <v>-387.577</v>
-      </c>
-      <c r="I158" s="12" t="n">
-        <v>-391.593</v>
-      </c>
-      <c r="K158" s="12" t="n">
-        <v>-439.589</v>
-      </c>
-      <c r="M158" s="12" t="n">
-        <v>-445.849</v>
-      </c>
-      <c r="O158" s="12" t="n">
-        <v>-235.157</v>
-      </c>
-      <c r="P158" s="12" t="n">
-        <v>-218.471</v>
-      </c>
-      <c r="Q158" s="12" t="n">
-        <v>-255.405</v>
-      </c>
-      <c r="R158" s="12" t="n">
-        <v>-193.214</v>
-      </c>
-      <c r="S158" s="12" t="n">
-        <v>-195.399</v>
-      </c>
-      <c r="T158" s="12" t="n">
-        <v>-170.352</v>
-      </c>
-      <c r="U158" s="12" t="n">
-        <v>-254.886</v>
-      </c>
-      <c r="V158" s="12" t="n">
-        <v>-461.199</v>
-      </c>
-      <c r="W158" s="12" t="n">
-        <v>-391.593</v>
-      </c>
-      <c r="X158" s="12" t="n">
-        <v>-445.849</v>
+      <c r="A158" s="20" t="inlineStr">
+        <is>
+          <t>Purchase Of More Investments In Subsidiaries Inv CF</t>
+        </is>
+      </c>
+      <c r="P158" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="22" t="n">
+        <v>-30.375</v>
+      </c>
+      <c r="R158" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
-        </is>
-      </c>
-      <c r="C159" s="22" t="n">
-        <v>16.823</v>
+          <t>Purchase Of Memberships Inv CF</t>
+        </is>
       </c>
       <c r="E159" s="22" t="n">
-        <v>32.303</v>
-      </c>
-      <c r="G159" s="22" t="n">
-        <v>-37.015</v>
+        <v>-7.421</v>
       </c>
       <c r="I159" s="22" t="n">
-        <v>-20.008</v>
-      </c>
-      <c r="K159" s="22" t="n">
-        <v>-0.516</v>
-      </c>
-      <c r="M159" s="22" t="n">
-        <v>99.691</v>
-      </c>
-      <c r="O159" s="22" t="n">
-        <v>-9.27</v>
-      </c>
-      <c r="P159" s="22" t="n">
-        <v>2.384</v>
-      </c>
-      <c r="Q159" s="22" t="n">
-        <v>-4.726</v>
-      </c>
-      <c r="R159" s="22" t="n">
-        <v>-10.875</v>
-      </c>
-      <c r="S159" s="22" t="n">
-        <v>26.384</v>
-      </c>
-      <c r="T159" s="22" t="n">
-        <v>47.339</v>
+        <v>0</v>
       </c>
       <c r="U159" s="22" t="n">
-        <v>15.643</v>
+        <v>0</v>
       </c>
       <c r="V159" s="22" t="n">
-        <v>32.303</v>
+        <v>-7.421</v>
       </c>
       <c r="W159" s="22" t="n">
-        <v>-20.008</v>
-      </c>
-      <c r="X159" s="22" t="n">
-        <v>99.691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C160" s="22" t="n">
+        <v>2.679</v>
+      </c>
+      <c r="E160" s="22" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="G160" s="22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I160" s="22" t="n">
+        <v>-0.705</v>
+      </c>
+      <c r="K160" s="22" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M160" s="22" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="O160" s="22" t="n">
+        <v>-0.476</v>
+      </c>
+      <c r="P160" s="22" t="n">
+        <v>-5.472</v>
+      </c>
+      <c r="Q160" s="22" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="R160" s="22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S160" s="22" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="T160" s="22" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="U160" s="22" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="V160" s="22" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="W160" s="22" t="n">
+        <v>-0.705</v>
+      </c>
+      <c r="X160" s="22" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="n">
+        <v>-106.509</v>
+      </c>
+      <c r="E161" s="12" t="n">
+        <v>-264.885</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>-141.804</v>
+      </c>
+      <c r="I161" s="12" t="n">
+        <v>-211.063</v>
+      </c>
+      <c r="K161" s="12" t="n">
+        <v>-362.543</v>
+      </c>
+      <c r="M161" s="12" t="n">
+        <v>-908.806</v>
+      </c>
+      <c r="O161" s="12" t="n">
+        <v>-35.065</v>
+      </c>
+      <c r="P161" s="12" t="n">
+        <v>-375.448</v>
+      </c>
+      <c r="Q161" s="12" t="n">
+        <v>-567.592</v>
+      </c>
+      <c r="R161" s="12" t="n">
+        <v>-307.865</v>
+      </c>
+      <c r="S161" s="12" t="n">
+        <v>-277.738</v>
+      </c>
+      <c r="T161" s="12" t="n">
+        <v>-119.259</v>
+      </c>
+      <c r="U161" s="12" t="n">
+        <v>-61.802</v>
+      </c>
+      <c r="V161" s="12" t="n">
+        <v>-264.885</v>
+      </c>
+      <c r="W161" s="12" t="n">
+        <v>-211.063</v>
+      </c>
+      <c r="X161" s="12" t="n">
+        <v>-908.806</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="E162" s="22" t="n">
+        <v>-139.242</v>
+      </c>
+      <c r="I162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="22" t="n">
+        <v>-45.581</v>
+      </c>
+      <c r="P162" s="22" t="n">
+        <v>-32.789</v>
+      </c>
+      <c r="Q162" s="22" t="n">
+        <v>-70.048</v>
+      </c>
+      <c r="R162" s="22" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="S162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" s="22" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="U162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" s="22" t="n">
+        <v>-139.242</v>
+      </c>
+      <c r="W162" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="C163" s="22" t="n">
+        <v>-2.258</v>
+      </c>
+      <c r="E163" s="22" t="n">
+        <v>-4.449</v>
+      </c>
+      <c r="G163" s="22" t="n">
+        <v>-1.533</v>
+      </c>
+      <c r="I163" s="22" t="n">
+        <v>-4.308</v>
+      </c>
+      <c r="K163" s="22" t="n">
+        <v>-2.329</v>
+      </c>
+      <c r="M163" s="22" t="n">
+        <v>-4.405</v>
+      </c>
+      <c r="O163" s="22" t="n">
+        <v>-4.058</v>
+      </c>
+      <c r="P163" s="22" t="n">
+        <v>-2.833</v>
+      </c>
+      <c r="Q163" s="22" t="n">
+        <v>-2.357</v>
+      </c>
+      <c r="R163" s="22" t="n">
+        <v>-3.375</v>
+      </c>
+      <c r="S163" s="22" t="n">
+        <v>-4.006</v>
+      </c>
+      <c r="T163" s="22" t="n">
+        <v>-4.157</v>
+      </c>
+      <c r="U163" s="22" t="n">
+        <v>-4.686</v>
+      </c>
+      <c r="V163" s="22" t="n">
+        <v>-4.449</v>
+      </c>
+      <c r="W163" s="22" t="n">
+        <v>-4.308</v>
+      </c>
+      <c r="X163" s="22" t="n">
+        <v>-4.405</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="n">
+        <v>-317.362</v>
+      </c>
+      <c r="E164" s="22" t="n">
+        <v>-317.508</v>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>-386.044</v>
+      </c>
+      <c r="I164" s="22" t="n">
+        <v>-387.285</v>
+      </c>
+      <c r="K164" s="22" t="n">
+        <v>-437.26</v>
+      </c>
+      <c r="M164" s="22" t="n">
+        <v>-441.444</v>
+      </c>
+      <c r="O164" s="22" t="n">
+        <v>-185.517</v>
+      </c>
+      <c r="P164" s="22" t="n">
+        <v>-182.849</v>
+      </c>
+      <c r="Q164" s="22" t="n">
+        <v>-182.999</v>
+      </c>
+      <c r="R164" s="22" t="n">
+        <v>-189.799</v>
+      </c>
+      <c r="S164" s="22" t="n">
+        <v>-191.393</v>
+      </c>
+      <c r="T164" s="22" t="n">
+        <v>-166.072</v>
+      </c>
+      <c r="U164" s="22" t="n">
+        <v>-250.2</v>
+      </c>
+      <c r="V164" s="22" t="n">
+        <v>-317.508</v>
+      </c>
+      <c r="W164" s="22" t="n">
+        <v>-387.285</v>
+      </c>
+      <c r="X164" s="22" t="n">
+        <v>-441.444</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="n">
+        <v>-319.621</v>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v>-461.199</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>-387.577</v>
+      </c>
+      <c r="I165" s="12" t="n">
+        <v>-391.593</v>
+      </c>
+      <c r="K165" s="12" t="n">
+        <v>-439.589</v>
+      </c>
+      <c r="M165" s="12" t="n">
+        <v>-445.849</v>
+      </c>
+      <c r="O165" s="12" t="n">
+        <v>-235.157</v>
+      </c>
+      <c r="P165" s="12" t="n">
+        <v>-218.471</v>
+      </c>
+      <c r="Q165" s="12" t="n">
+        <v>-255.405</v>
+      </c>
+      <c r="R165" s="12" t="n">
+        <v>-193.214</v>
+      </c>
+      <c r="S165" s="12" t="n">
+        <v>-195.399</v>
+      </c>
+      <c r="T165" s="12" t="n">
+        <v>-170.352</v>
+      </c>
+      <c r="U165" s="12" t="n">
+        <v>-254.886</v>
+      </c>
+      <c r="V165" s="12" t="n">
+        <v>-461.199</v>
+      </c>
+      <c r="W165" s="12" t="n">
+        <v>-391.593</v>
+      </c>
+      <c r="X165" s="12" t="n">
+        <v>-445.849</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="C166" s="22" t="n">
+        <v>16.823</v>
+      </c>
+      <c r="E166" s="22" t="n">
+        <v>32.303</v>
+      </c>
+      <c r="G166" s="22" t="n">
+        <v>-37.015</v>
+      </c>
+      <c r="I166" s="22" t="n">
+        <v>-20.008</v>
+      </c>
+      <c r="K166" s="22" t="n">
+        <v>-0.516</v>
+      </c>
+      <c r="M166" s="22" t="n">
+        <v>99.691</v>
+      </c>
+      <c r="O166" s="22" t="n">
+        <v>-9.27</v>
+      </c>
+      <c r="P166" s="22" t="n">
+        <v>2.384</v>
+      </c>
+      <c r="Q166" s="22" t="n">
+        <v>-4.726</v>
+      </c>
+      <c r="R166" s="22" t="n">
+        <v>-10.875</v>
+      </c>
+      <c r="S166" s="22" t="n">
+        <v>26.384</v>
+      </c>
+      <c r="T166" s="22" t="n">
+        <v>47.339</v>
+      </c>
+      <c r="U166" s="22" t="n">
+        <v>15.643</v>
+      </c>
+      <c r="V166" s="22" t="n">
+        <v>32.303</v>
+      </c>
+      <c r="W166" s="22" t="n">
+        <v>-20.008</v>
+      </c>
+      <c r="X166" s="22" t="n">
+        <v>99.691</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C160" s="22" t="n">
+      <c r="C167" s="22" t="n">
         <v>-52.816</v>
       </c>
-      <c r="E160" s="22" t="n">
+      <c r="E167" s="22" t="n">
         <v>538.587</v>
       </c>
-      <c r="G160" s="22" t="n">
+      <c r="G167" s="22" t="n">
         <v>464.837</v>
       </c>
-      <c r="I160" s="22" t="n">
+      <c r="I167" s="22" t="n">
         <v>1522.882</v>
       </c>
-      <c r="K160" s="22" t="n">
+      <c r="K167" s="22" t="n">
         <v>-474.53</v>
       </c>
-      <c r="M160" s="22" t="n">
+      <c r="M167" s="22" t="n">
         <v>1028.676</v>
       </c>
-      <c r="O160" s="22" t="n">
+      <c r="O167" s="22" t="n">
         <v>47.491</v>
       </c>
-      <c r="P160" s="22" t="n">
+      <c r="P167" s="22" t="n">
         <v>-334.268</v>
       </c>
-      <c r="Q160" s="22" t="n">
+      <c r="Q167" s="22" t="n">
         <v>-326.129</v>
       </c>
-      <c r="R160" s="22" t="n">
+      <c r="R167" s="22" t="n">
         <v>257.311</v>
       </c>
-      <c r="S160" s="22" t="n">
+      <c r="S167" s="22" t="n">
         <v>623.828</v>
       </c>
-      <c r="T160" s="22" t="n">
+      <c r="T167" s="22" t="n">
         <v>-178.578</v>
       </c>
-      <c r="U160" s="22" t="n">
+      <c r="U167" s="22" t="n">
         <v>-263.451</v>
       </c>
-      <c r="V160" s="22" t="n">
+      <c r="V167" s="22" t="n">
         <v>538.587</v>
       </c>
-      <c r="W160" s="22" t="n">
+      <c r="W167" s="22" t="n">
         <v>1522.882</v>
       </c>
-      <c r="X160" s="22" t="n">
+      <c r="X167" s="22" t="n">
         <v>1028.676</v>
       </c>
     </row>
@@ -9906,7 +10377,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11306,7 +11777,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11358,7 +11829,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11410,7 +11881,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11462,7 +11933,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11514,7 +11985,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11566,7 +12037,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11618,7 +12089,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11628,43 +12099,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11688,7 +12159,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11740,7 +12211,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -11792,7 +12263,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11844,7 +12315,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11896,7 +12367,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11948,7 +12419,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12018,7 +12489,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12070,7 +12541,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12080,49 +12551,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12132,49 +12603,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12184,49 +12655,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12236,43 +12707,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12296,7 +12767,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12348,7 +12819,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12400,7 +12871,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12452,7 +12923,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -14970,24 +15441,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
